--- a/Prototypes/Lentil/CanadaCEData.xlsx
+++ b/Prototypes/Lentil/CanadaCEData.xlsx
@@ -2,22 +2,29 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHubRepos\ApsimX\Prototypes\Lentil\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4396C275-7F4F-4C06-8EE5-A02ECE2FB26F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB95CAD5-3748-4125-984B-BA3E179F43BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{A5017088-8F3F-41C2-9D3D-102B2E5948D4}"/>
+    <workbookView xWindow="-16320" yWindow="-5925" windowWidth="16440" windowHeight="28320" activeTab="2" xr2:uid="{A5017088-8F3F-41C2-9D3D-102B2E5948D4}"/>
   </bookViews>
   <sheets>
     <sheet name="Roberts_etal_1988" sheetId="1" r:id="rId1"/>
     <sheet name="Summerfield_etal_1985" sheetId="5" r:id="rId2"/>
     <sheet name="Roberts_etal_1986" sheetId="6" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="7" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Roberts_etal_1986!$A$2:$G$91</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="8" r:id="rId5"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="65">
   <si>
     <t>Duration of Preliminary Treatment</t>
   </si>
@@ -189,6 +196,51 @@
   <si>
     <t>No Vern treatment so day from sowing</t>
   </si>
+  <si>
+    <t>Start</t>
+  </si>
+  <si>
+    <t>End</t>
+  </si>
+  <si>
+    <t>Flower</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>ponit</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Column Labels</t>
+  </si>
+  <si>
+    <t>Sum of x</t>
+  </si>
+  <si>
+    <t>TtEnv1bud</t>
+  </si>
+  <si>
+    <t>TtEvn2bud</t>
+  </si>
+  <si>
+    <t>TtFirstBud</t>
+  </si>
+  <si>
+    <t>TtButToFlower</t>
+  </si>
 </sst>
 </file>
 
@@ -235,9 +287,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -253,6 +310,603 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Hamish Brown" refreshedDate="45608.461907638892" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="66" xr:uid="{6B15166F-67B2-4CAB-8D10-1BE078DACBDB}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:D67" sheet="Sheet1"/>
+  </cacheSource>
+  <cacheFields count="4">
+    <cacheField name="treat" numFmtId="0">
+      <sharedItems count="22">
+        <s v="A"/>
+        <s v="b"/>
+        <s v="c"/>
+        <s v="d"/>
+        <s v="e"/>
+        <s v="f"/>
+        <s v="g"/>
+        <s v="h"/>
+        <s v="i"/>
+        <s v="j"/>
+        <s v="k"/>
+        <s v="l"/>
+        <s v="m"/>
+        <s v="n"/>
+        <s v="o"/>
+        <s v="p"/>
+        <s v="q"/>
+        <s v="r"/>
+        <s v="s"/>
+        <s v="t"/>
+        <s v="u"/>
+        <s v="v"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="ponit" numFmtId="0">
+      <sharedItems count="3">
+        <s v="Start"/>
+        <s v="End"/>
+        <s v="Flower"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="x" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-0.18056234526043699" maxValue="81.283411918691698"/>
+    </cacheField>
+    <cacheField name="y" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="4.4951350669420999E-2" maxValue="0.99082995600271195"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="66">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="0.41868386608424402"/>
+    <n v="0.98875624871871604"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="45.0506993834071"/>
+    <n v="0.99082995600271195"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="75.787299134246894"/>
+    <n v="0.98967877249144398"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="0.19869742797218401"/>
+    <n v="0.94382066768643602"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="41.462318452052401"/>
+    <n v="0.94602053206755699"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="64.409505937268307"/>
+    <n v="0.94516108684339095"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="0.189235645687794"/>
+    <n v="0.89887720183558495"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="37.4528882090423"/>
+    <n v="0.90122687776954202"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="63.558339772601798"/>
+    <n v="0.90212180467727399"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="0.17937962247488601"/>
+    <n v="0.852061091574282"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="33.442669484175099"/>
+    <n v="0.85268793465062298"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="2"/>
+    <n v="62.285730055351401"/>
+    <n v="0.85722564773784504"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="0"/>
+    <n v="0.38162521880371902"/>
+    <n v="0.81272767413621705"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="1"/>
+    <n v="29.644552378849699"/>
+    <n v="0.81163168435494204"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="2"/>
+    <n v="57.854856259757398"/>
+    <n v="0.81057511866651899"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="0"/>
+    <n v="0.37176919559081101"/>
+    <n v="0.76591156387491499"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="25.003548168356598"/>
+    <n v="0.76686168451263903"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="2"/>
+    <n v="59.319855550123698"/>
+    <n v="0.76932174790658003"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="0"/>
+    <n v="0.151388516550234"/>
+    <n v="0.71910333843218199"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="1"/>
+    <n v="21.4147729960733"/>
+    <n v="0.72017961616703197"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="2"/>
+    <n v="55.098717928500399"/>
+    <n v="0.71891804519577995"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="0"/>
+    <n v="0.35284563102203398"/>
+    <n v="0.67602463217321296"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="1"/>
+    <n v="18.037705202403199"/>
+    <n v="0.67910759623421002"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="2"/>
+    <n v="52.984009587939298"/>
+    <n v="0.67405342753063202"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="0"/>
+    <n v="0.13325343383848601"/>
+    <n v="0.63296169555138504"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="1"/>
+    <n v="13.3970952328386"/>
+    <n v="0.636210240802359"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="2"/>
+    <n v="51.291533281819099"/>
+    <n v="0.63479097345970004"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="0"/>
+    <n v="0.124185892482614"/>
+    <n v="0.58989087411098595"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="1"/>
+    <n v="9.3864822670430303"/>
+    <n v="0.58579865327298797"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="2"/>
+    <n v="50.228265497610799"/>
+    <n v="0.58426899847034497"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="0"/>
+    <n v="-9.6194786557962403E-2"/>
+    <n v="0.54308264866825395"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="1"/>
+    <n v="48.744342642675697"/>
+    <n v="0.535635437528582"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="2"/>
+    <n v="48.746708088246798"/>
+    <n v="0.54687130399129502"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="0"/>
+    <n v="0.105262327913834"/>
+    <n v="0.50000394240928503"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="1"/>
+    <n v="45.789112642517999"/>
+    <n v="0.49829293677952402"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="2"/>
+    <n v="49.577767965559097"/>
+    <n v="0.494405721224354"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <x v="0"/>
+    <n v="0.30553671960008399"/>
+    <n v="0.45130730291895899"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <x v="1"/>
+    <n v="41.5695519846088"/>
+    <n v="0.45537981171053199"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <x v="2"/>
+    <n v="46.200700171888997"/>
+    <n v="0.453333701291533"/>
+  </r>
+  <r>
+    <x v="13"/>
+    <x v="0"/>
+    <n v="-0.124974374339647"/>
+    <n v="0.40637960670524897"/>
+  </r>
+  <r>
+    <x v="13"/>
+    <x v="1"/>
+    <n v="37.558544777884599"/>
+    <n v="0.40309557977070898"/>
+  </r>
+  <r>
+    <x v="13"/>
+    <x v="2"/>
+    <n v="46.821629634302099"/>
+    <n v="0.40274864775361502"/>
+  </r>
+  <r>
+    <x v="14"/>
+    <x v="0"/>
+    <n v="0.28661315503130402"/>
+    <n v="0.36142037121725801"/>
+  </r>
+  <r>
+    <x v="14"/>
+    <x v="1"/>
+    <n v="33.340166842760901"/>
+    <n v="0.36580038793307301"/>
+  </r>
+  <r>
+    <x v="14"/>
+    <x v="2"/>
+    <n v="48.286628924668399"/>
+    <n v="0.36149527699367601"/>
+  </r>
+  <r>
+    <x v="15"/>
+    <x v="0"/>
+    <n v="6.7415198776274096E-2"/>
+    <n v="0.32023007900588102"/>
+  </r>
+  <r>
+    <x v="15"/>
+    <x v="1"/>
+    <n v="29.752180152334599"/>
+    <n v="0.32286360840836997"/>
+  </r>
+  <r>
+    <x v="15"/>
+    <x v="2"/>
+    <n v="48.908741109867002"/>
+    <n v="0.31652815668711398"/>
+  </r>
+  <r>
+    <x v="16"/>
+    <x v="0"/>
+    <n v="-0.15257123933578101"/>
+    <n v="0.275294497973601"/>
+  </r>
+  <r>
+    <x v="16"/>
+    <x v="1"/>
+    <n v="25.5322252534969"/>
+    <n v="0.27807783892892601"/>
+  </r>
+  <r>
+    <x v="16"/>
+    <x v="2"/>
+    <n v="66.5845331398924"/>
+    <n v="0.27654029930771201"/>
+  </r>
+  <r>
+    <x v="17"/>
+    <x v="0"/>
+    <n v="-0.162033021620171"/>
+    <n v="0.23035103212274999"/>
+  </r>
+  <r>
+    <x v="17"/>
+    <x v="1"/>
+    <n v="21.7321369435289"/>
+    <n v="0.22765836658098401"/>
+  </r>
+  <r>
+    <x v="17"/>
+    <x v="2"/>
+    <n v="68.890842571712398"/>
+    <n v="0.23151010045258799"/>
+  </r>
+  <r>
+    <x v="18"/>
+    <x v="0"/>
+    <n v="-0.17149480390456101"/>
+    <n v="0.185407566271899"/>
+  </r>
+  <r>
+    <x v="18"/>
+    <x v="1"/>
+    <n v="17.934019838203501"/>
+    <n v="0.18660211628530399"/>
+  </r>
+  <r>
+    <x v="18"/>
+    <x v="2"/>
+    <n v="73.092662387838402"/>
+    <n v="0.190154227051235"/>
+  </r>
+  <r>
+    <x v="19"/>
+    <x v="0"/>
+    <n v="-0.18056234526043699"/>
+    <n v="0.14233674483150099"/>
+  </r>
+  <r>
+    <x v="19"/>
+    <x v="1"/>
+    <n v="13.503540283537999"/>
+    <n v="0.14182423162443"/>
+  </r>
+  <r>
+    <x v="19"/>
+    <x v="2"/>
+    <n v="76.871855928594996"/>
+    <n v="0.14132354564521399"/>
+  </r>
+  <r>
+    <x v="20"/>
+    <x v="0"/>
+    <n v="2.0500528282841601E-2"/>
+    <n v="9.7385394162080099E-2"/>
+  </r>
+  <r>
+    <x v="20"/>
+    <x v="1"/>
+    <n v="9.4937157995994408"/>
+    <n v="9.51579329159635E-2"/>
+  </r>
+  <r>
+    <x v="20"/>
+    <x v="2"/>
+    <n v="81.283411918691698"/>
+    <n v="9.6214498604387105E-2"/>
+  </r>
+  <r>
+    <x v="21"/>
+    <x v="0"/>
+    <n v="1.14329869269695E-2"/>
+    <n v="5.4314572721681303E-2"/>
+  </r>
+  <r>
+    <x v="21"/>
+    <x v="1"/>
+    <n v="9.4617822843900898E-3"/>
+    <n v="4.4951350669420999E-2"/>
+  </r>
+  <r>
+    <x v="21"/>
+    <x v="2"/>
+    <n v="79.590935612571499"/>
+    <n v="5.6952044533455197E-2"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{52ED00D8-EABF-46CF-A307-A86388A41F4F}" name="PivotTable2" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="G4:J27" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="4">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="23">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="22">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i>
+      <x v="21"/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="1"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of x" fld="2" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -573,12 +1227,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8957C88F-B319-4213-B505-5B5C10A69141}">
   <dimension ref="A1:K194"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="13.44140625" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -610,7 +1264,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -645,7 +1299,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -683,7 +1337,7 @@
         <v>716.98831674599751</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f t="shared" ref="A4:A35" si="3">A3</f>
         <v>Precoz</v>
@@ -725,7 +1379,7 @@
         <v>636.84552141929919</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f t="shared" si="3"/>
         <v>Precoz</v>
@@ -767,7 +1421,7 @@
         <v>567.74123755949768</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f t="shared" si="3"/>
         <v>Precoz</v>
@@ -809,7 +1463,7 @@
         <v>515.75075724794397</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f t="shared" si="3"/>
         <v>Precoz</v>
@@ -851,7 +1505,7 @@
         <v>710.9130246646464</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f t="shared" si="3"/>
         <v>Precoz</v>
@@ -893,7 +1547,7 @@
         <v>652.54435309389794</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f t="shared" si="3"/>
         <v>Precoz</v>
@@ -935,7 +1589,7 @@
         <v>620.9130246646464</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f t="shared" si="3"/>
         <v>Precoz</v>
@@ -977,7 +1631,7 @@
         <v>713.22371267849394</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f t="shared" si="3"/>
         <v>Precoz</v>
@@ -1019,7 +1673,7 @@
         <v>710.96495023799162</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f t="shared" si="3"/>
         <v>Precoz</v>
@@ -1061,7 +1715,7 @@
         <v>662.16789268714797</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f t="shared" si="3"/>
         <v>Precoz</v>
@@ -1103,7 +1757,7 @@
         <v>765.21419299004754</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f t="shared" si="3"/>
         <v>Precoz</v>
@@ -1145,7 +1799,7 @@
         <v>868.11769796624753</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f t="shared" si="3"/>
         <v>Precoz</v>
@@ -1184,7 +1838,7 @@
         <v>715.10533967979131</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f t="shared" si="3"/>
         <v>Precoz</v>
@@ -1226,7 +1880,7 @@
         <v>568.13433145824274</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f t="shared" si="3"/>
         <v>Precoz</v>
@@ -1268,7 +1922,7 @@
         <v>535.53372565988752</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f t="shared" si="3"/>
         <v>Precoz</v>
@@ -1310,7 +1964,7 @@
         <v>471.34073561228888</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f t="shared" si="3"/>
         <v>Precoz</v>
@@ -1352,7 +2006,7 @@
         <v>715.10533967979131</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f t="shared" si="3"/>
         <v>Precoz</v>
@@ -1394,7 +2048,7 @@
         <v>632.48742535698807</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f t="shared" si="3"/>
         <v>Precoz</v>
@@ -1436,7 +2090,7 @@
         <v>619.03004759844123</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f t="shared" si="3"/>
         <v>Precoz</v>
@@ -1478,7 +2132,7 @@
         <v>662.73839896148763</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f t="shared" si="3"/>
         <v>Precoz</v>
@@ -1520,7 +2174,7 @@
         <v>715.10533967979131</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f t="shared" si="3"/>
         <v>Precoz</v>
@@ -1562,7 +2216,7 @@
         <v>690.66137602769288</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f t="shared" si="3"/>
         <v>Precoz</v>
@@ -1604,7 +2258,7 @@
         <v>666.1784681955852</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f t="shared" si="3"/>
         <v>Precoz</v>
@@ -1646,7 +2300,7 @@
         <v>835.91018606663761</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f t="shared" si="3"/>
         <v>Precoz</v>
@@ -1685,7 +2339,7 @@
         <v>773.35787970575325</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f t="shared" si="3"/>
         <v>Precoz</v>
@@ -1727,7 +2381,7 @@
         <v>765.76376460406675</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f t="shared" si="3"/>
         <v>Precoz</v>
@@ -1769,7 +2423,7 @@
         <v>510.01300735612062</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f t="shared" si="3"/>
         <v>Precoz</v>
@@ -1811,7 +2465,7 @@
         <v>515.92386845521196</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f t="shared" si="3"/>
         <v>Precoz</v>
@@ -1853,7 +2507,7 @@
         <v>773.35787970575325</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
         <f t="shared" si="3"/>
         <v>Precoz</v>
@@ -1895,7 +2549,7 @@
         <v>709.57163998268993</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
         <f t="shared" si="3"/>
         <v>Precoz</v>
@@ -1937,7 +2591,7 @@
         <v>639.55000432713007</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="str">
         <f t="shared" si="3"/>
         <v>Precoz</v>
@@ -1979,7 +2633,7 @@
         <v>669.35095629597436</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="str">
         <f t="shared" si="3"/>
         <v>Precoz</v>
@@ -2021,7 +2675,7 @@
         <v>773.35787970575325</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="str">
         <f t="shared" ref="A36:A67" si="16">A35</f>
         <v>Precoz</v>
@@ -2063,7 +2717,7 @@
         <v>662.99872782345233</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="str">
         <f t="shared" si="16"/>
         <v>Precoz</v>
@@ -2105,7 +2759,7 @@
         <v>759.63221981825814</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="str">
         <f t="shared" si="16"/>
         <v>Precoz</v>
@@ -2147,7 +2801,7 @@
         <v>813.15883167459742</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="str">
         <f t="shared" si="16"/>
         <v>Precoz</v>
@@ -2186,7 +2840,7 @@
         <v>751.03028991778319</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="str">
         <f t="shared" si="16"/>
         <v>Precoz</v>
@@ -2228,7 +2882,7 @@
         <v>608.68498485503994</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="str">
         <f t="shared" si="16"/>
         <v>Precoz</v>
@@ -2270,7 +2924,7 @@
         <v>545.31847684984757</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="str">
         <f t="shared" si="16"/>
         <v>Precoz</v>
@@ -2312,7 +2966,7 @@
         <v>407.02336650800436</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="str">
         <f t="shared" si="16"/>
         <v>Precoz</v>
@@ -2354,7 +3008,7 @@
         <v>751.03028991778319</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="str">
         <f t="shared" si="16"/>
         <v>Precoz</v>
@@ -2396,7 +3050,7 @@
         <v>648.76720034616983</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="str">
         <f t="shared" si="16"/>
         <v>Precoz</v>
@@ -2438,7 +3092,7 @@
         <v>597.98398961488317</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="str">
         <f t="shared" si="16"/>
         <v>Precoz</v>
@@ -2480,7 +3134,7 @@
         <v>618.16572912159188</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="str">
         <f t="shared" si="16"/>
         <v>Precoz</v>
@@ -2522,7 +3176,7 @@
         <v>751.03028991778319</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="str">
         <f t="shared" si="16"/>
         <v>Precoz</v>
@@ -2564,7 +3218,7 @@
         <v>640.58892254435239</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="str">
         <f t="shared" si="16"/>
         <v>Precoz</v>
@@ -2606,7 +3260,7 @@
         <v>631.49329294677568</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="str">
         <f t="shared" si="16"/>
         <v>Precoz</v>
@@ -2648,7 +3302,7 @@
         <v>675.40069234097768</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="str">
         <f t="shared" si="16"/>
         <v>Precoz</v>
@@ -2687,7 +3341,7 @@
         <v>629.2274818007304</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="str">
         <f t="shared" si="16"/>
         <v>Precoz</v>
@@ -2728,7 +3382,7 @@
         <v>579.66861033646001</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="str">
         <f t="shared" si="16"/>
         <v>Precoz</v>
@@ -2769,7 +3423,7 @@
         <v>505.01068414762199</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="str">
         <f t="shared" si="16"/>
         <v>Precoz</v>
@@ -2810,7 +3464,7 @@
         <v>477.48578465104322</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="str">
         <f t="shared" si="16"/>
         <v>Precoz</v>
@@ -2851,7 +3505,7 @@
         <v>629.27963492810761</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="str">
         <f t="shared" si="16"/>
         <v>Precoz</v>
@@ -2892,7 +3546,7 @@
         <v>577.37242403389882</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="str">
         <f t="shared" si="16"/>
         <v>Precoz</v>
@@ -2933,7 +3587,7 @@
         <v>606.80924269312914</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="str">
         <f t="shared" si="16"/>
         <v>Precoz</v>
@@ -2974,7 +3628,7 @@
         <v>675.13744522110596</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="str">
         <f t="shared" si="16"/>
         <v>Precoz</v>
@@ -3015,7 +3669,7 @@
         <v>629.2274818007304</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="str">
         <f t="shared" si="16"/>
         <v>Precoz</v>
@@ -3056,7 +3710,7 @@
         <v>623.37003368222759</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="str">
         <f t="shared" si="16"/>
         <v>Precoz</v>
@@ -3097,7 +3751,7 @@
         <v>714.70971714171833</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="str">
         <f t="shared" si="16"/>
         <v>Precoz</v>
@@ -3138,7 +3792,7 @@
         <v>812.29147803411479</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="str">
         <f t="shared" si="16"/>
         <v>Precoz</v>
@@ -3177,7 +3831,7 @@
         <v>639.50528557458847</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="str">
         <f t="shared" si="16"/>
         <v>Precoz</v>
@@ -3218,7 +3872,7 @@
         <v>565.79951613487242</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="str">
         <f t="shared" si="16"/>
         <v>Precoz</v>
@@ -3259,7 +3913,7 @@
         <v>472.8879953641644</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" t="str">
         <f t="shared" si="16"/>
         <v>Precoz</v>
@@ -3300,7 +3954,7 @@
         <v>427.26596066784839</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" t="str">
         <f t="shared" si="16"/>
         <v>Precoz</v>
@@ -3341,7 +3995,7 @@
         <v>633.45552279888352</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" t="str">
         <f t="shared" ref="A68:A98" si="27">A67</f>
         <v>Precoz</v>
@@ -3382,7 +4036,7 @@
         <v>593.69999058346161</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" t="str">
         <f t="shared" si="27"/>
         <v>Precoz</v>
@@ -3423,7 +4077,7 @@
         <v>580.73631668537882</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" t="str">
         <f t="shared" si="27"/>
         <v>Precoz</v>
@@ -3464,7 +4118,7 @@
         <v>624.91762123791113</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" t="str">
         <f t="shared" si="27"/>
         <v>Precoz</v>
@@ -3505,7 +4159,7 @@
         <v>627.40576002317766</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" t="str">
         <f t="shared" si="27"/>
         <v>Precoz</v>
@@ -3546,7 +4200,7 @@
         <v>609.44878635326404</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" t="str">
         <f t="shared" si="27"/>
         <v>Precoz</v>
@@ -3587,7 +4241,7 @@
         <v>603.94011227409237</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" t="str">
         <f t="shared" si="27"/>
         <v>Precoz</v>
@@ -3628,7 +4282,7 @@
         <v>659.12138060917562</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" t="str">
         <f t="shared" si="27"/>
         <v>Precoz</v>
@@ -3667,7 +4321,7 @@
         <v>569.04125384810015</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" t="str">
         <f t="shared" si="27"/>
         <v>Precoz</v>
@@ -3708,7 +4362,7 @@
         <v>532.63366267067215</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" t="str">
         <f t="shared" si="27"/>
         <v>Precoz</v>
@@ -3749,7 +4403,7 @@
         <v>479.47151714895909</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" t="str">
         <f t="shared" si="27"/>
         <v>Precoz</v>
@@ -3790,7 +4444,7 @@
         <v>456.70559052551209</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" t="str">
         <f t="shared" si="27"/>
         <v>Precoz</v>
@@ -3831,7 +4485,7 @@
         <v>569.04125384810015</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" t="str">
         <f t="shared" si="27"/>
         <v>Precoz</v>
@@ -3872,7 +4526,7 @@
         <v>572.63366267067215</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" t="str">
         <f t="shared" si="27"/>
         <v>Precoz</v>
@@ -3913,7 +4567,7 @@
         <v>580.23135924088001</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" t="str">
         <f t="shared" si="27"/>
         <v>Precoz</v>
@@ -3954,7 +4608,7 @@
         <v>648.81163521784526</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" t="str">
         <f t="shared" si="27"/>
         <v>Precoz</v>
@@ -3995,7 +4649,7 @@
         <v>569.04125384810015</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" t="str">
         <f t="shared" si="27"/>
         <v>Precoz</v>
@@ -4036,7 +4690,7 @@
         <v>603.05487160913776</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" t="str">
         <f t="shared" si="27"/>
         <v>Precoz</v>
@@ -4077,7 +4731,7 @@
         <v>681.07377711781101</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" t="str">
         <f t="shared" si="27"/>
         <v>Precoz</v>
@@ -4118,7 +4772,7 @@
         <v>793.02372460250979</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" t="str">
         <f t="shared" si="27"/>
         <v>Precoz</v>
@@ -4157,7 +4811,7 @@
         <v>556.47064575712284</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" t="str">
         <f t="shared" si="27"/>
         <v>Precoz</v>
@@ -4198,7 +4852,7 @@
         <v>510.48426351815846</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" t="str">
         <f t="shared" si="27"/>
         <v>Precoz</v>
@@ -4239,7 +4893,7 @@
         <v>495.38955488754169</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" t="str">
         <f t="shared" si="27"/>
         <v>Precoz</v>
@@ -4280,7 +4934,7 @@
         <v>396.15845134185219</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" t="str">
         <f t="shared" si="27"/>
         <v>Precoz</v>
@@ -4321,7 +4975,7 @@
         <v>556.47064575712284</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" t="str">
         <f t="shared" si="27"/>
         <v>Precoz</v>
@@ -4362,7 +5016,7 @@
         <v>550.48426351815851</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" t="str">
         <f t="shared" si="27"/>
         <v>Precoz</v>
@@ -4403,7 +5057,7 @@
         <v>529.26301111875273</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" t="str">
         <f t="shared" si="27"/>
         <v>Precoz</v>
@@ -4444,7 +5098,7 @@
         <v>550.03190757306515</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" t="str">
         <f t="shared" si="27"/>
         <v>Precoz</v>
@@ -4485,7 +5139,7 @@
         <v>556.47064575712284</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" t="str">
         <f t="shared" si="27"/>
         <v>Precoz</v>
@@ -4526,7 +5180,7 @@
         <v>590.48426351815851</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" t="str">
         <f t="shared" si="27"/>
         <v>Precoz</v>
@@ -4567,7 +5221,7 @@
         <v>562.97131577993787</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" t="str">
         <f t="shared" si="27"/>
         <v>Precoz</v>
@@ -4608,7 +5262,7 @@
         <v>675.16899061967808</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>17</v>
       </c>
@@ -4646,7 +5300,7 @@
         <v>1249.337979094068</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>17</v>
       </c>
@@ -4687,7 +5341,7 @@
         <v>1169.024390243902</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>17</v>
       </c>
@@ -4728,7 +5382,7 @@
         <v>1078.6411149825781</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>17</v>
       </c>
@@ -4769,7 +5423,7 @@
         <v>1063.4843205574907</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>17</v>
       </c>
@@ -4810,7 +5464,7 @@
         <v>1249.337979094068</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>17</v>
       </c>
@@ -4851,7 +5505,7 @@
         <v>1143.7979094076652</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>17</v>
       </c>
@@ -4892,7 +5546,7 @@
         <v>1073.2055749128913</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>17</v>
       </c>
@@ -4933,7 +5587,7 @@
         <v>1087.7351916376297</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>17</v>
       </c>
@@ -4974,7 +5628,7 @@
         <v>1249.337979094068</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>17</v>
       </c>
@@ -5015,7 +5669,7 @@
         <v>963.0313588850172</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>17</v>
       </c>
@@ -5056,7 +5710,7 @@
         <v>1248.3972125435532</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>17</v>
       </c>
@@ -5097,7 +5751,7 @@
         <v>1262.5087108013927</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>17</v>
       </c>
@@ -5135,7 +5789,7 @@
         <v>1239.3031358884919</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>17</v>
       </c>
@@ -5176,7 +5830,7 @@
         <v>1043.5888501742152</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>17</v>
       </c>
@@ -5217,7 +5871,7 @@
         <v>1133.83275261324</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>17</v>
       </c>
@@ -5258,7 +5912,7 @@
         <v>928.01393728222911</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>17</v>
       </c>
@@ -5299,7 +5953,7 @@
         <v>1244.3205574912799</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>17</v>
       </c>
@@ -5340,7 +5994,7 @@
         <v>1038.432055749128</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>17</v>
       </c>
@@ -5381,7 +6035,7 @@
         <v>1218.7108013937277</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>17</v>
       </c>
@@ -5422,7 +6076,7 @@
         <v>1097.7700348432045</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>17</v>
       </c>
@@ -5463,7 +6117,7 @@
         <v>1244.3205574912799</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>17</v>
       </c>
@@ -5504,7 +6158,7 @@
         <v>1178.7804878048773</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>17</v>
       </c>
@@ -5545,7 +6199,7 @@
         <v>1193.2055749128913</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>17</v>
       </c>
@@ -5586,7 +6240,7 @@
         <v>1147.1080139372821</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>17</v>
       </c>
@@ -5624,7 +6278,7 @@
         <v>1962.2299651567789</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>17</v>
       </c>
@@ -5665,7 +6319,7 @@
         <v>1741.84668989547</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>17</v>
       </c>
@@ -5706,7 +6360,7 @@
         <v>1285.191637630661</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>17</v>
       </c>
@@ -5747,7 +6401,7 @@
         <v>1203.9721254355386</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>17</v>
       </c>
@@ -5788,7 +6442,7 @@
         <v>1970.17421602786</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>17</v>
       </c>
@@ -5829,7 +6483,7 @@
         <v>1694.4599303135883</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>17</v>
       </c>
@@ -5870,7 +6524,7 @@
         <v>1270.1393728222995</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>17</v>
       </c>
@@ -5911,7 +6565,7 @@
         <v>1324.8083623693369</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>17</v>
       </c>
@@ -5952,7 +6606,7 @@
         <v>1962.2299651567789</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>17</v>
       </c>
@@ -5993,7 +6647,7 @@
         <v>1384.9128919860623</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>17</v>
       </c>
@@ -6034,7 +6688,7 @@
         <v>1310.696864111497</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>17</v>
       </c>
@@ -6075,7 +6729,7 @@
         <v>1334.4250871080126</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>17</v>
       </c>
@@ -6113,7 +6767,7 @@
         <v>1970.17421602786</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>17</v>
       </c>
@@ -6154,7 +6808,7 @@
         <v>1622.6829268292663</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>17</v>
       </c>
@@ -6195,7 +6849,7 @@
         <v>1452.0209059233432</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>17</v>
       </c>
@@ -6236,7 +6890,7 @@
         <v>1362.8571428571415</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>17</v>
       </c>
@@ -6277,7 +6931,7 @@
         <v>1970.17421602786</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>17</v>
       </c>
@@ -6318,7 +6972,7 @@
         <v>1630.9059233449461</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>17</v>
       </c>
@@ -6359,7 +7013,7 @@
         <v>1349.5818815330999</v>
       </c>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>17</v>
       </c>
@@ -6400,7 +7054,7 @@
         <v>1316.8641114982561</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>17</v>
       </c>
@@ -6441,7 +7095,7 @@
         <v>1970.17421602786</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>17</v>
       </c>
@@ -6482,7 +7136,7 @@
         <v>1392.8571428571415</v>
       </c>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>17</v>
       </c>
@@ -6523,7 +7177,7 @@
         <v>1406.0278745644596</v>
       </c>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>17</v>
       </c>
@@ -6564,7 +7218,7 @@
         <v>1493.3101045296155</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>17</v>
       </c>
@@ -6602,7 +7256,7 @@
         <v>886.92041522491309</v>
       </c>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>17</v>
       </c>
@@ -6642,7 +7296,7 @@
         <v>802.24913494809653</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>17</v>
       </c>
@@ -6682,7 +7336,7 @@
         <v>677.75086505190245</v>
       </c>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>17</v>
       </c>
@@ -6722,7 +7376,7 @@
         <v>682.83737024221432</v>
       </c>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>17</v>
       </c>
@@ -6762,7 +7416,7 @@
         <v>886.92041522491309</v>
       </c>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>17</v>
       </c>
@@ -6802,7 +7456,7 @@
         <v>827.30103806228362</v>
       </c>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>17</v>
       </c>
@@ -6842,7 +7496,7 @@
         <v>772.83737024221432</v>
       </c>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>17</v>
       </c>
@@ -6882,7 +7536,7 @@
         <v>877.99307958477482</v>
       </c>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>17</v>
       </c>
@@ -6922,7 +7576,7 @@
         <v>886.92041522491309</v>
       </c>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>17</v>
       </c>
@@ -6962,7 +7616,7 @@
         <v>852.35294117647072</v>
       </c>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>17</v>
       </c>
@@ -7002,7 +7656,7 @@
         <v>952.62975778546559</v>
       </c>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>17</v>
       </c>
@@ -7042,7 +7696,7 @@
         <v>983.46020761245597</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>17</v>
       </c>
@@ -7080,7 +7734,7 @@
         <v>886.92041522491309</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>17</v>
       </c>
@@ -7120,7 +7774,7 @@
         <v>812.21453287197164</v>
       </c>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>17</v>
       </c>
@@ -7160,7 +7814,7 @@
         <v>697.6816608996528</v>
       </c>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>17</v>
       </c>
@@ -7200,7 +7854,7 @@
         <v>593.1487889273352</v>
       </c>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>17</v>
       </c>
@@ -7240,7 +7894,7 @@
         <v>886.92041522491309</v>
       </c>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>17</v>
       </c>
@@ -7280,7 +7934,7 @@
         <v>822.31833910034607</v>
       </c>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>17</v>
       </c>
@@ -7320,7 +7974,7 @@
         <v>777.82006920415199</v>
       </c>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>17</v>
       </c>
@@ -7360,7 +8014,7 @@
         <v>788.30449826989559</v>
       </c>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>17</v>
       </c>
@@ -7400,7 +8054,7 @@
         <v>886.92041522491309</v>
       </c>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>17</v>
       </c>
@@ -7440,7 +8094,7 @@
         <v>822.45674740484401</v>
       </c>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>17</v>
       </c>
@@ -7480,7 +8134,7 @@
         <v>823.07958477508555</v>
       </c>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>17</v>
       </c>
@@ -7520,7 +8174,7 @@
         <v>903.73702422145197</v>
       </c>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>17</v>
       </c>
@@ -7558,7 +8212,7 @@
         <v>1049.2733564013843</v>
       </c>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>17</v>
       </c>
@@ -7598,7 +8252,7 @@
         <v>933.04498269896123</v>
       </c>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>17</v>
       </c>
@@ -7638,7 +8292,7 @@
         <v>779.48096885813106</v>
       </c>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>17</v>
       </c>
@@ -7678,7 +8332,7 @@
         <v>777.92387543252437</v>
       </c>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>17</v>
       </c>
@@ -7718,7 +8372,7 @@
         <v>1049.2733564013843</v>
       </c>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>17</v>
       </c>
@@ -7758,7 +8412,7 @@
         <v>933.59861591695346</v>
       </c>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>17</v>
       </c>
@@ -7798,7 +8452,7 @@
         <v>867.92387543252437</v>
       </c>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>17</v>
       </c>
@@ -7838,7 +8492,7 @@
         <v>939.03114186851235</v>
       </c>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>17</v>
       </c>
@@ -7878,7 +8532,7 @@
         <v>1049.2733564013843</v>
       </c>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>17</v>
       </c>
@@ -7918,7 +8572,7 @@
         <v>934.1522491349474</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>17</v>
       </c>
@@ -7958,7 +8612,7 @@
         <v>964.2560553633208</v>
       </c>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>17</v>
       </c>
@@ -7998,7 +8652,7 @@
         <v>1052.8027681660894</v>
       </c>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>17</v>
       </c>
@@ -8036,7 +8690,7 @@
         <v>1072.941176470586</v>
       </c>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>17</v>
       </c>
@@ -8076,7 +8730,7 @@
         <v>877.82006920415108</v>
       </c>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>17</v>
       </c>
@@ -8116,7 +8770,7 @@
         <v>866.26297577854439</v>
       </c>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>17</v>
       </c>
@@ -8156,7 +8810,7 @@
         <v>706.92041522491172</v>
       </c>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>17</v>
       </c>
@@ -8196,7 +8850,7 @@
         <v>1065.0519031141848</v>
       </c>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>17</v>
       </c>
@@ -8236,7 +8890,7 @@
         <v>909.93079584774978</v>
       </c>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>17</v>
       </c>
@@ -8276,7 +8930,7 @@
         <v>844.2560553633208</v>
       </c>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>17</v>
       </c>
@@ -8316,7 +8970,7 @@
         <v>852.24913494809539</v>
       </c>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>17</v>
       </c>
@@ -8356,7 +9010,7 @@
         <v>1065.0519031141848</v>
       </c>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>17</v>
       </c>
@@ -8396,7 +9050,7 @@
         <v>949.93079584774978</v>
       </c>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>17</v>
       </c>
@@ -8436,7 +9090,7 @@
         <v>964.2560553633208</v>
       </c>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>17</v>
       </c>
@@ -8485,9 +9139,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F02E8EA-B070-4490-9798-E1D250B1FF21}">
   <dimension ref="A1:K74"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -8519,7 +9173,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -8554,7 +9208,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
@@ -8592,7 +9246,7 @@
         <v>799.77794226499009</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -8630,7 +9284,7 @@
         <v>853.54398741013165</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -8668,7 +9322,7 @@
         <v>958.6882887203675</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -8706,7 +9360,7 @@
         <v>939.13421376663177</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -8744,7 +9398,7 @@
         <v>758.5783238262411</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -8782,7 +9436,7 @@
         <v>839.82409490693738</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -8820,7 +9474,7 @@
         <v>788.51794811041691</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -8858,7 +9512,7 @@
         <v>915.32889999576491</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -8896,7 +9550,7 @@
         <v>684.71014676434334</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -8934,7 +9588,7 @@
         <v>705.58161641627612</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -8972,7 +9626,7 @@
         <v>766.78752859968245</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -9010,7 +9664,7 @@
         <v>722.25268378332771</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
@@ -9048,7 +9702,7 @@
         <v>698.738378099177</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -9087,7 +9741,7 @@
         <v>681.87775728858026</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -9126,7 +9780,7 @@
         <v>787.63035239283806</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -9165,7 +9819,7 @@
         <v>780.40077433204408</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -9204,7 +9858,7 @@
         <v>645.76801127356293</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>15</v>
       </c>
@@ -9243,7 +9897,7 @@
         <v>683.17845184163912</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>15</v>
       </c>
@@ -9282,7 +9936,7 @@
         <v>622.2630394260201</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>15</v>
       </c>
@@ -9321,7 +9975,7 @@
         <v>664.89443531618633</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>15</v>
       </c>
@@ -9360,7 +10014,7 @@
         <v>599.43422531108388</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>15</v>
       </c>
@@ -9399,7 +10053,7 @@
         <v>611.15250134481039</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>15</v>
       </c>
@@ -9438,7 +10092,7 @@
         <v>616.31550426198771</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>15</v>
       </c>
@@ -9477,7 +10131,7 @@
         <v>622.16481788802628</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>21</v>
       </c>
@@ -9515,7 +10169,7 @@
         <v>1109.6000000000013</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>21</v>
       </c>
@@ -9553,7 +10207,7 @@
         <v>1139.512195121958</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>21</v>
       </c>
@@ -9591,7 +10245,7 @@
         <v>1511.0489510489519</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>21</v>
       </c>
@@ -9629,7 +10283,7 @@
         <v>1189.1402714932176</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>21</v>
       </c>
@@ -9667,7 +10321,7 @@
         <v>929.09090909091253</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>21</v>
       </c>
@@ -9705,7 +10359,7 @@
         <v>977.62114537445257</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>21</v>
       </c>
@@ -9743,7 +10397,7 @@
         <v>1045.7674418604704</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>21</v>
       </c>
@@ -9781,7 +10435,7 @@
         <v>1110.2661596958228</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>21</v>
       </c>
@@ -9819,7 +10473,7 @@
         <v>793.47826086956763</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>21</v>
       </c>
@@ -9857,7 +10511,7 @@
         <v>838.83636363636651</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>21</v>
       </c>
@@ -9895,7 +10549,7 @@
         <v>1051.8897637795278</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>21</v>
       </c>
@@ -9933,7 +10587,7 @@
         <v>1103.9024390243926</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>21</v>
       </c>
@@ -9971,7 +10625,7 @@
         <v>767.57751589839484</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>21</v>
       </c>
@@ -10010,7 +10664,7 @@
         <v>1135.0080450523017</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>21</v>
       </c>
@@ -10049,7 +10703,7 @@
         <v>1476.5164252752882</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>21</v>
       </c>
@@ -10088,7 +10742,7 @@
         <v>1145.7250353851937</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>21</v>
       </c>
@@ -10127,7 +10781,7 @@
         <v>896.78905015088731</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>21</v>
       </c>
@@ -10166,7 +10820,7 @@
         <v>882.41216884401638</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>21</v>
       </c>
@@ -10205,7 +10859,7 @@
         <v>874.01388394446519</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>21</v>
       </c>
@@ -10244,7 +10898,7 @@
         <v>983.09544910710599</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>21</v>
       </c>
@@ -10283,7 +10937,7 @@
         <v>612.85262118838887</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>21</v>
       </c>
@@ -10322,7 +10976,7 @@
         <v>621.36213254299264</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>21</v>
       </c>
@@ -10361,7 +11015,7 @@
         <v>850.06005569178706</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>21</v>
       </c>
@@ -10400,7 +11054,7 @@
         <v>773.85338494978521</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>17</v>
       </c>
@@ -10438,7 +11092,7 @@
         <v>1034.444444444445</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>17</v>
       </c>
@@ -10476,7 +11130,7 @@
         <v>1280.0000000000014</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>17</v>
       </c>
@@ -10514,7 +11168,7 @@
         <v>1450.400000000009</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>17</v>
       </c>
@@ -10552,7 +11206,7 @@
         <v>1633.3333333333342</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>17</v>
       </c>
@@ -10590,7 +11244,7 @@
         <v>1016.2962962962968</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>17</v>
       </c>
@@ -10628,7 +11282,7 @@
         <v>1354.1818181818262</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>17</v>
       </c>
@@ -10666,7 +11320,7 @@
         <v>1237.0491803278724</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>17</v>
       </c>
@@ -10704,7 +11358,7 @@
         <v>1507.6923076923167</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>17</v>
       </c>
@@ -10727,7 +11381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>17</v>
       </c>
@@ -10750,7 +11404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>17</v>
       </c>
@@ -10773,7 +11427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>17</v>
       </c>
@@ -10796,7 +11450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>17</v>
       </c>
@@ -10819,7 +11473,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>17</v>
       </c>
@@ -10843,7 +11497,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>17</v>
       </c>
@@ -10867,7 +11521,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>17</v>
       </c>
@@ -10891,7 +11545,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>17</v>
       </c>
@@ -10930,7 +11584,7 @@
         <v>991.20689655172816</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>17</v>
       </c>
@@ -10954,7 +11608,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>17</v>
       </c>
@@ -10993,7 +11647,7 @@
         <v>1078.6986301369841</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>17</v>
       </c>
@@ -11032,7 +11686,7 @@
         <v>1269.9999999999998</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>17</v>
       </c>
@@ -11071,7 +11725,7 @@
         <v>872.70270270270441</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>17</v>
       </c>
@@ -11110,7 +11764,7 @@
         <v>966.66666666666913</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>17</v>
       </c>
@@ -11149,7 +11803,7 @@
         <v>1041.3333333333339</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>17</v>
       </c>
@@ -11180,10 +11834,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{211B18F4-0F9D-4AAE-8CDD-2B69E84EFAD9}">
-  <dimension ref="A1:M91"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:Q92"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -11215,7 +11869,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -11255,8 +11909,20 @@
       <c r="M2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N2" t="s">
+        <v>61</v>
+      </c>
+      <c r="O2" t="s">
+        <v>62</v>
+      </c>
+      <c r="P2" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>22</v>
       </c>
@@ -11282,7 +11948,7 @@
         <v>64.58715596330272</v>
       </c>
       <c r="I3">
-        <v>69.577981651376163</v>
+        <v>69.577981651376206</v>
       </c>
       <c r="J3">
         <f>E3*MIN(G3,I3)</f>
@@ -11290,17 +11956,33 @@
       </c>
       <c r="K3">
         <f>F3*MAX(0,I3-G3)</f>
-        <v>522.28211009174345</v>
+        <v>522.28211009174436</v>
       </c>
       <c r="L3">
         <f>J3+K3</f>
-        <v>1478.5321100917436</v>
+        <v>1478.5321100917445</v>
       </c>
       <c r="M3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N3">
+        <f>E3*MIN(G3,H3)</f>
+        <v>956.25</v>
+      </c>
+      <c r="O3">
+        <f>F3*MAX(0,H3-G3)</f>
+        <v>416.2270642201828</v>
+      </c>
+      <c r="P3">
+        <f>N3+O3</f>
+        <v>1372.4770642201829</v>
+      </c>
+      <c r="Q3">
+        <f>L3-P3</f>
+        <v>106.05504587156156</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>22</v>
       </c>
@@ -11343,8 +12025,24 @@
       <c r="M4" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N4">
+        <f t="shared" ref="N4:N67" si="3">E4*MIN(G4,H4)</f>
+        <v>871.25</v>
+      </c>
+      <c r="O4">
+        <f t="shared" ref="O4:O67" si="4">F4*MAX(0,H4-G4)</f>
+        <v>413.88761467889634</v>
+      </c>
+      <c r="P4">
+        <f t="shared" ref="P4:P67" si="5">N4+O4</f>
+        <v>1285.1376146788964</v>
+      </c>
+      <c r="Q4">
+        <f t="shared" ref="Q4:Q67" si="6">L4-P4</f>
+        <v>143.48623853211257</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>22</v>
       </c>
@@ -11387,8 +12085,24 @@
       <c r="M5" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N5">
+        <f t="shared" si="3"/>
+        <v>786.25</v>
+      </c>
+      <c r="O5">
+        <f t="shared" si="4"/>
+        <v>424.02522935779621</v>
+      </c>
+      <c r="P5">
+        <f t="shared" si="5"/>
+        <v>1210.2752293577962</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" si="6"/>
+        <v>124.77064220183479</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>22</v>
       </c>
@@ -11431,8 +12145,24 @@
       <c r="M6" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N6">
+        <f t="shared" si="3"/>
+        <v>701.25</v>
+      </c>
+      <c r="O6">
+        <f t="shared" si="4"/>
+        <v>396.73165137614416</v>
+      </c>
+      <c r="P6">
+        <f t="shared" si="5"/>
+        <v>1097.9816513761441</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="6"/>
+        <v>143.48623853211234</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>22</v>
       </c>
@@ -11475,8 +12205,24 @@
       <c r="M7" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N7">
+        <f t="shared" si="3"/>
+        <v>616.25</v>
+      </c>
+      <c r="O7">
+        <f t="shared" si="4"/>
+        <v>381.91513761467837</v>
+      </c>
+      <c r="P7">
+        <f t="shared" si="5"/>
+        <v>998.16513761467832</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="6"/>
+        <v>124.77064220183502</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>22</v>
       </c>
@@ -11519,8 +12265,24 @@
       <c r="M8" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N8">
+        <f t="shared" si="3"/>
+        <v>531.25</v>
+      </c>
+      <c r="O8">
+        <f t="shared" si="4"/>
+        <v>404.52981651376098</v>
+      </c>
+      <c r="P8">
+        <f t="shared" si="5"/>
+        <v>935.77981651376103</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="6"/>
+        <v>131.00917431192624</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>22</v>
       </c>
@@ -11563,8 +12325,24 @@
       <c r="M9" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N9">
+        <f t="shared" si="3"/>
+        <v>446.25</v>
+      </c>
+      <c r="O9">
+        <f t="shared" si="4"/>
+        <v>370.9977064220177</v>
+      </c>
+      <c r="P9">
+        <f t="shared" si="5"/>
+        <v>817.2477064220177</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="6"/>
+        <v>162.20183486238329</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>22</v>
       </c>
@@ -11607,8 +12385,24 @@
       <c r="M10" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N10">
+        <f t="shared" si="3"/>
+        <v>361.25</v>
+      </c>
+      <c r="O10">
+        <f t="shared" si="4"/>
+        <v>387.37385321100891</v>
+      </c>
+      <c r="P10">
+        <f t="shared" si="5"/>
+        <v>748.62385321100896</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="6"/>
+        <v>155.9633027522915</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>22</v>
       </c>
@@ -11651,8 +12445,24 @@
       <c r="M11" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N11">
+        <f t="shared" si="3"/>
+        <v>276.25</v>
+      </c>
+      <c r="O11">
+        <f t="shared" si="4"/>
+        <v>385.03440366972234</v>
+      </c>
+      <c r="P11">
+        <f t="shared" si="5"/>
+        <v>661.28440366972234</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="6"/>
+        <v>131.00917431192624</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
@@ -11695,8 +12505,24 @@
       <c r="M12" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N12">
+        <f t="shared" si="3"/>
+        <v>191.25</v>
+      </c>
+      <c r="O12">
+        <f t="shared" si="4"/>
+        <v>463.795871559631</v>
+      </c>
+      <c r="P12">
+        <f t="shared" si="5"/>
+        <v>655.045871559631</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" si="6"/>
+        <v>131.00917431192624</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>22</v>
       </c>
@@ -11739,8 +12565,24 @@
       <c r="M13" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <f t="shared" si="4"/>
+        <v>605.1376146788964</v>
+      </c>
+      <c r="P13">
+        <f t="shared" si="5"/>
+        <v>605.1376146788964</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="6"/>
+        <v>143.48623853211257</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>22</v>
       </c>
@@ -11783,8 +12625,24 @@
       <c r="M14" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N14">
+        <f t="shared" si="3"/>
+        <v>598.89908256880506</v>
+      </c>
+      <c r="O14">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <f t="shared" si="5"/>
+        <v>598.89908256880506</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="6"/>
+        <v>124.77064220183479</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>22</v>
       </c>
@@ -11827,8 +12685,24 @@
       <c r="M15" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N15">
+        <f t="shared" si="3"/>
+        <v>605.1376146788964</v>
+      </c>
+      <c r="O15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <f t="shared" si="5"/>
+        <v>605.1376146788964</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" si="6"/>
+        <v>143.48623853211257</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>22</v>
       </c>
@@ -11871,8 +12745,24 @@
       <c r="M16" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N16">
+        <f t="shared" si="3"/>
+        <v>605.1376146788964</v>
+      </c>
+      <c r="O16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <f t="shared" si="5"/>
+        <v>605.1376146788964</v>
+      </c>
+      <c r="Q16">
+        <f t="shared" si="6"/>
+        <v>137.247706422021</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>22</v>
       </c>
@@ -11915,8 +12805,24 @@
       <c r="M17" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N17">
+        <f t="shared" si="3"/>
+        <v>623.85321100917395</v>
+      </c>
+      <c r="O17">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <f t="shared" si="5"/>
+        <v>623.85321100917395</v>
+      </c>
+      <c r="Q17">
+        <f t="shared" si="6"/>
+        <v>124.77064220183502</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>22</v>
       </c>
@@ -11939,28 +12845,44 @@
         <v>29</v>
       </c>
       <c r="H18">
-        <v>36.403669724770559</v>
+        <v>28</v>
       </c>
       <c r="I18">
-        <v>27.889908256880638</v>
+        <v>36</v>
       </c>
       <c r="J18">
         <f t="shared" si="0"/>
-        <v>592.6605504587136</v>
+        <v>616.25</v>
       </c>
       <c r="K18">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>148.75</v>
       </c>
       <c r="L18">
         <f t="shared" si="2"/>
-        <v>592.6605504587136</v>
+        <v>765</v>
       </c>
       <c r="M18" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N18">
+        <f t="shared" si="3"/>
+        <v>595</v>
+      </c>
+      <c r="O18">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <f t="shared" si="5"/>
+        <v>595</v>
+      </c>
+      <c r="Q18">
+        <f>L18-P18</f>
+        <v>170</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>22</v>
       </c>
@@ -12003,8 +12925,24 @@
       <c r="M19" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N19">
+        <f t="shared" si="3"/>
+        <v>531.25</v>
+      </c>
+      <c r="O19">
+        <f t="shared" si="4"/>
+        <v>98.841743119265445</v>
+      </c>
+      <c r="P19">
+        <f t="shared" si="5"/>
+        <v>630.0917431192654</v>
+      </c>
+      <c r="Q19">
+        <f t="shared" si="6"/>
+        <v>124.77064220183479</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>22</v>
       </c>
@@ -12047,8 +12985,24 @@
       <c r="M20" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N20">
+        <f t="shared" si="3"/>
+        <v>446.25</v>
+      </c>
+      <c r="O20">
+        <f t="shared" si="4"/>
+        <v>190.08027522935677</v>
+      </c>
+      <c r="P20">
+        <f t="shared" si="5"/>
+        <v>636.33027522935674</v>
+      </c>
+      <c r="Q20">
+        <f t="shared" si="6"/>
+        <v>1409.9082568807348</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>22</v>
       </c>
@@ -12091,8 +13045,24 @@
       <c r="M21" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N21">
+        <f t="shared" si="3"/>
+        <v>361.25</v>
+      </c>
+      <c r="O21">
+        <f t="shared" si="4"/>
+        <v>942.60321100917406</v>
+      </c>
+      <c r="P21">
+        <f t="shared" si="5"/>
+        <v>1303.8532110091742</v>
+      </c>
+      <c r="Q21">
+        <f t="shared" si="6"/>
+        <v>1528.4403669724775</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>22</v>
       </c>
@@ -12135,8 +13105,24 @@
       <c r="M22" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N22">
+        <f t="shared" si="3"/>
+        <v>276.25</v>
+      </c>
+      <c r="O22">
+        <f t="shared" si="4"/>
+        <v>2044.4839449541266</v>
+      </c>
+      <c r="P22">
+        <f t="shared" si="5"/>
+        <v>2320.7339449541269</v>
+      </c>
+      <c r="Q22">
+        <f t="shared" si="6"/>
+        <v>623.85321100917372</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>22</v>
       </c>
@@ -12179,8 +13165,24 @@
       <c r="M23" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N23">
+        <f t="shared" si="3"/>
+        <v>191.25</v>
+      </c>
+      <c r="O23">
+        <f t="shared" si="4"/>
+        <v>1886.1811926605485</v>
+      </c>
+      <c r="P23">
+        <f t="shared" si="5"/>
+        <v>2077.4311926605487</v>
+      </c>
+      <c r="Q23">
+        <f t="shared" si="6"/>
+        <v>112.29357798165165</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>22</v>
       </c>
@@ -12223,8 +13225,24 @@
       <c r="M24" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N24">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <f t="shared" si="4"/>
+        <v>2177.2477064220175</v>
+      </c>
+      <c r="P24">
+        <f t="shared" si="5"/>
+        <v>2177.2477064220175</v>
+      </c>
+      <c r="Q24">
+        <f t="shared" si="6"/>
+        <v>536.51376146789107</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>17</v>
       </c>
@@ -12267,8 +13285,24 @@
       <c r="M25" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N25">
+        <f t="shared" si="3"/>
+        <v>956.25</v>
+      </c>
+      <c r="O25">
+        <f t="shared" si="4"/>
+        <v>206.21173011549581</v>
+      </c>
+      <c r="P25">
+        <f t="shared" si="5"/>
+        <v>1162.4617301154958</v>
+      </c>
+      <c r="Q25">
+        <f t="shared" si="6"/>
+        <v>285.9715799919768</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>17</v>
       </c>
@@ -12311,8 +13345,24 @@
       <c r="M26" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N26">
+        <f t="shared" si="3"/>
+        <v>871.25</v>
+      </c>
+      <c r="O26">
+        <f t="shared" si="4"/>
+        <v>214.18210658558701</v>
+      </c>
+      <c r="P26">
+        <f t="shared" si="5"/>
+        <v>1085.432106585587</v>
+      </c>
+      <c r="Q26">
+        <f t="shared" si="6"/>
+        <v>207.62283313274611</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>17</v>
       </c>
@@ -12355,8 +13405,24 @@
       <c r="M27" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N27">
+        <f t="shared" si="3"/>
+        <v>786.25</v>
+      </c>
+      <c r="O27">
+        <f t="shared" si="4"/>
+        <v>319.32790164903514</v>
+      </c>
+      <c r="P27">
+        <f t="shared" si="5"/>
+        <v>1105.5779016490351</v>
+      </c>
+      <c r="Q27">
+        <f t="shared" si="6"/>
+        <v>184.30934735330652</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>17</v>
       </c>
@@ -12399,8 +13465,24 @@
       <c r="M28" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N28">
+        <f t="shared" si="3"/>
+        <v>701.25</v>
+      </c>
+      <c r="O28">
+        <f t="shared" si="4"/>
+        <v>354.91013175397308</v>
+      </c>
+      <c r="P28">
+        <f t="shared" si="5"/>
+        <v>1056.160131753973</v>
+      </c>
+      <c r="Q28">
+        <f t="shared" si="6"/>
+        <v>170.72327442410528</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>17</v>
       </c>
@@ -12443,8 +13525,24 @@
       <c r="M29" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N29">
+        <f t="shared" si="3"/>
+        <v>616.25</v>
+      </c>
+      <c r="O29">
+        <f t="shared" si="4"/>
+        <v>441.29207047993071</v>
+      </c>
+      <c r="P29">
+        <f t="shared" si="5"/>
+        <v>1057.5420704799308</v>
+      </c>
+      <c r="Q29">
+        <f t="shared" si="6"/>
+        <v>189.29868457169346</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>17</v>
       </c>
@@ -12487,8 +13585,24 @@
       <c r="M30" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N30">
+        <f t="shared" si="3"/>
+        <v>531.25</v>
+      </c>
+      <c r="O30">
+        <f t="shared" si="4"/>
+        <v>504.80023120288661</v>
+      </c>
+      <c r="P30">
+        <f t="shared" si="5"/>
+        <v>1036.0502312028866</v>
+      </c>
+      <c r="Q30">
+        <f t="shared" si="6"/>
+        <v>198.39794345558721</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>17</v>
       </c>
@@ -12531,8 +13645,24 @@
       <c r="M31" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N31">
+        <f t="shared" si="3"/>
+        <v>446.25</v>
+      </c>
+      <c r="O31">
+        <f t="shared" si="4"/>
+        <v>545.12053693967596</v>
+      </c>
+      <c r="P31">
+        <f t="shared" si="5"/>
+        <v>991.37053693967596</v>
+      </c>
+      <c r="Q31">
+        <f t="shared" si="6"/>
+        <v>184.43497814657508</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>17</v>
       </c>
@@ -12575,8 +13705,24 @@
       <c r="M32" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N32">
+        <f t="shared" si="3"/>
+        <v>361.25</v>
+      </c>
+      <c r="O32">
+        <f t="shared" si="4"/>
+        <v>645.33981018137263</v>
+      </c>
+      <c r="P32">
+        <f t="shared" si="5"/>
+        <v>1006.5898101813726</v>
+      </c>
+      <c r="Q32">
+        <f t="shared" si="6"/>
+        <v>179.88534870463047</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>17</v>
       </c>
@@ -12619,8 +13765,24 @@
       <c r="M33" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N33">
+        <f t="shared" si="3"/>
+        <v>276.25</v>
+      </c>
+      <c r="O33">
+        <f t="shared" si="4"/>
+        <v>685.53448512489103</v>
+      </c>
+      <c r="P33">
+        <f t="shared" si="5"/>
+        <v>961.78448512489103</v>
+      </c>
+      <c r="Q33">
+        <f t="shared" si="6"/>
+        <v>189.29868457169346</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>17</v>
       </c>
@@ -12663,8 +13825,24 @@
       <c r="M34" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N34">
+        <f t="shared" si="3"/>
+        <v>191.25</v>
+      </c>
+      <c r="O34">
+        <f t="shared" si="4"/>
+        <v>795.16709423365057</v>
+      </c>
+      <c r="P34">
+        <f t="shared" si="5"/>
+        <v>986.41709423365057</v>
+      </c>
+      <c r="Q34">
+        <f t="shared" si="6"/>
+        <v>184.49779354321083</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>17</v>
       </c>
@@ -12707,8 +13885,24 @@
       <c r="M35" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N35">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <f t="shared" si="4"/>
+        <v>927.83725005806332</v>
+      </c>
+      <c r="P35">
+        <f t="shared" si="5"/>
+        <v>927.83725005806332</v>
+      </c>
+      <c r="Q35">
+        <f t="shared" si="6"/>
+        <v>216.91053820654247</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>17</v>
       </c>
@@ -12751,8 +13945,24 @@
       <c r="M36" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N36">
+        <f t="shared" si="3"/>
+        <v>929.40763497392322</v>
+      </c>
+      <c r="O36">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <f t="shared" si="5"/>
+        <v>929.40763497392322</v>
+      </c>
+      <c r="Q36">
+        <f t="shared" si="6"/>
+        <v>258.29691096049464</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>17</v>
       </c>
@@ -12795,8 +14005,24 @@
       <c r="M37" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N37">
+        <f t="shared" si="3"/>
+        <v>871.25</v>
+      </c>
+      <c r="O37">
+        <f t="shared" si="4"/>
+        <v>64.08920314182366</v>
+      </c>
+      <c r="P37">
+        <f t="shared" si="5"/>
+        <v>935.33920314182365</v>
+      </c>
+      <c r="Q37">
+        <f t="shared" si="6"/>
+        <v>226.13542788370296</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>17</v>
       </c>
@@ -12839,8 +14065,24 @@
       <c r="M38" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N38">
+        <f t="shared" si="3"/>
+        <v>786.25</v>
+      </c>
+      <c r="O38">
+        <f t="shared" si="4"/>
+        <v>242.84566943265557</v>
+      </c>
+      <c r="P38">
+        <f t="shared" si="5"/>
+        <v>1029.0956694326555</v>
+      </c>
+      <c r="Q38">
+        <f t="shared" si="6"/>
+        <v>424.40774054601729</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>17</v>
       </c>
@@ -12883,8 +14125,24 @@
       <c r="M39" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N39">
+        <f t="shared" si="3"/>
+        <v>701.25</v>
+      </c>
+      <c r="O39">
+        <f t="shared" si="4"/>
+        <v>366.2527976605208</v>
+      </c>
+      <c r="P39">
+        <f t="shared" si="5"/>
+        <v>1067.5027976605209</v>
+      </c>
+      <c r="Q39">
+        <f t="shared" si="6"/>
+        <v>608.9683494858632</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>17</v>
       </c>
@@ -12927,8 +14185,24 @@
       <c r="M40" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N40">
+        <f t="shared" si="3"/>
+        <v>616.25</v>
+      </c>
+      <c r="O40">
+        <f t="shared" si="4"/>
+        <v>415.79799307446871</v>
+      </c>
+      <c r="P40">
+        <f t="shared" si="5"/>
+        <v>1032.0479930744686</v>
+      </c>
+      <c r="Q40">
+        <f t="shared" si="6"/>
+        <v>322.93395409725326</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>17</v>
       </c>
@@ -12971,8 +14245,24 @@
       <c r="M41" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N41">
+        <f t="shared" si="3"/>
+        <v>531.25</v>
+      </c>
+      <c r="O41">
+        <f t="shared" si="4"/>
+        <v>599.04127341060996</v>
+      </c>
+      <c r="P41">
+        <f t="shared" si="5"/>
+        <v>1130.2912734106098</v>
+      </c>
+      <c r="Q41">
+        <f t="shared" si="6"/>
+        <v>867.26526044636057</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>17</v>
       </c>
@@ -13015,8 +14305,24 @@
       <c r="M42" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N42">
+        <f t="shared" si="3"/>
+        <v>446.25</v>
+      </c>
+      <c r="O42">
+        <f t="shared" si="4"/>
+        <v>810.08485357150232</v>
+      </c>
+      <c r="P42">
+        <f t="shared" si="5"/>
+        <v>1256.3348535715022</v>
+      </c>
+      <c r="Q42">
+        <f t="shared" si="6"/>
+        <v>673.47976182935327</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>17</v>
       </c>
@@ -13059,8 +14365,24 @@
       <c r="M43" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N43">
+        <f t="shared" si="3"/>
+        <v>361.25</v>
+      </c>
+      <c r="O43">
+        <f t="shared" si="4"/>
+        <v>891.85434745887972</v>
+      </c>
+      <c r="P43">
+        <f t="shared" si="5"/>
+        <v>1253.1043474588796</v>
+      </c>
+      <c r="Q43">
+        <f t="shared" si="6"/>
+        <v>890.3903000358896</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>17</v>
       </c>
@@ -13103,8 +14425,24 @@
       <c r="M44" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N44">
+        <f t="shared" si="3"/>
+        <v>276.25</v>
+      </c>
+      <c r="O44">
+        <f t="shared" si="4"/>
+        <v>918.33731867992572</v>
+      </c>
+      <c r="P44">
+        <f t="shared" si="5"/>
+        <v>1194.5873186799258</v>
+      </c>
+      <c r="Q44">
+        <f t="shared" si="6"/>
+        <v>1268.799222989363</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>17</v>
       </c>
@@ -13147,8 +14485,24 @@
       <c r="M45" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N45">
+        <f t="shared" si="3"/>
+        <v>191.25</v>
+      </c>
+      <c r="O45">
+        <f t="shared" si="4"/>
+        <v>967.94532949050915</v>
+      </c>
+      <c r="P45">
+        <f t="shared" si="5"/>
+        <v>1159.1953294905093</v>
+      </c>
+      <c r="Q45">
+        <f t="shared" si="6"/>
+        <v>1070.2756487405195</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>17</v>
       </c>
@@ -13191,8 +14545,24 @@
       <c r="M46" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N46">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O46">
+        <f t="shared" si="4"/>
+        <v>1156.0904541711532</v>
+      </c>
+      <c r="P46">
+        <f t="shared" si="5"/>
+        <v>1156.0904541711532</v>
+      </c>
+      <c r="Q46">
+        <f t="shared" si="6"/>
+        <v>705.76687569941578</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>15</v>
       </c>
@@ -13235,8 +14605,24 @@
       <c r="M47" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N47">
+        <f t="shared" si="3"/>
+        <v>956.25</v>
+      </c>
+      <c r="O47">
+        <f t="shared" si="4"/>
+        <v>48.357223312257851</v>
+      </c>
+      <c r="P47">
+        <f t="shared" si="5"/>
+        <v>1004.6072233122578</v>
+      </c>
+      <c r="Q47">
+        <f t="shared" si="6"/>
+        <v>115.90909090909201</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>15</v>
       </c>
@@ -13279,8 +14665,24 @@
       <c r="M48" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N48">
+        <f t="shared" si="3"/>
+        <v>871.25</v>
+      </c>
+      <c r="O48">
+        <f t="shared" si="4"/>
+        <v>70.383965554827071</v>
+      </c>
+      <c r="P48">
+        <f t="shared" si="5"/>
+        <v>941.63396555482711</v>
+      </c>
+      <c r="Q48">
+        <f t="shared" si="6"/>
+        <v>146.08313349320622</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>15</v>
       </c>
@@ -13323,8 +14725,24 @@
       <c r="M49" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N49">
+        <f t="shared" si="3"/>
+        <v>786.25</v>
+      </c>
+      <c r="O49">
+        <f t="shared" si="4"/>
+        <v>199.91924642104411</v>
+      </c>
+      <c r="P49">
+        <f t="shared" si="5"/>
+        <v>986.16924642104414</v>
+      </c>
+      <c r="Q49">
+        <f t="shared" si="6"/>
+        <v>154.60722331225998</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>15</v>
       </c>
@@ -13367,8 +14785,24 @@
       <c r="M50" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N50">
+        <f t="shared" si="3"/>
+        <v>701.25</v>
+      </c>
+      <c r="O50">
+        <f t="shared" si="4"/>
+        <v>230.65538478308144</v>
+      </c>
+      <c r="P50">
+        <f t="shared" si="5"/>
+        <v>931.90538478308144</v>
+      </c>
+      <c r="Q50">
+        <f t="shared" si="6"/>
+        <v>163.19308189811841</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>15</v>
       </c>
@@ -13411,8 +14845,24 @@
       <c r="M51" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N51">
+        <f t="shared" si="3"/>
+        <v>616.25</v>
+      </c>
+      <c r="O51">
+        <f t="shared" si="4"/>
+        <v>295.79672625535773</v>
+      </c>
+      <c r="P51">
+        <f t="shared" si="5"/>
+        <v>912.04672625535773</v>
+      </c>
+      <c r="Q51">
+        <f t="shared" si="6"/>
+        <v>146.02136472640154</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>15</v>
       </c>
@@ -13455,8 +14905,24 @@
       <c r="M52" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N52">
+        <f t="shared" si="3"/>
+        <v>531.25</v>
+      </c>
+      <c r="O52">
+        <f t="shared" si="4"/>
+        <v>317.82346849792691</v>
+      </c>
+      <c r="P52">
+        <f t="shared" si="5"/>
+        <v>849.07346849792691</v>
+      </c>
+      <c r="Q52">
+        <f t="shared" si="6"/>
+        <v>137.62081244095759</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>15</v>
       </c>
@@ -13499,8 +14965,24 @@
       <c r="M53" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N53">
+        <f t="shared" si="3"/>
+        <v>446.25</v>
+      </c>
+      <c r="O53">
+        <f t="shared" si="4"/>
+        <v>370.20955962502512</v>
+      </c>
+      <c r="P53">
+        <f t="shared" si="5"/>
+        <v>816.45955962502512</v>
+      </c>
+      <c r="Q53">
+        <f t="shared" si="6"/>
+        <v>146.02136472640143</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>15</v>
       </c>
@@ -13543,8 +15025,24 @@
       <c r="M54" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N54">
+        <f t="shared" si="3"/>
+        <v>361.25</v>
+      </c>
+      <c r="O54">
+        <f t="shared" si="4"/>
+        <v>375.06458469587943</v>
+      </c>
+      <c r="P54">
+        <f t="shared" si="5"/>
+        <v>736.31458469587938</v>
+      </c>
+      <c r="Q54">
+        <f t="shared" si="6"/>
+        <v>176.01010101010138</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>15</v>
       </c>
@@ -13587,8 +15085,24 @@
       <c r="M55" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N55">
+        <f t="shared" si="3"/>
+        <v>276.25</v>
+      </c>
+      <c r="O55">
+        <f t="shared" si="4"/>
+        <v>431.62006758229717</v>
+      </c>
+      <c r="P55">
+        <f t="shared" si="5"/>
+        <v>707.87006758229722</v>
+      </c>
+      <c r="Q55">
+        <f t="shared" si="6"/>
+        <v>163.1313131313135</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>15</v>
       </c>
@@ -13631,8 +15145,24 @@
       <c r="M56" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N56">
+        <f t="shared" si="3"/>
+        <v>191.25</v>
+      </c>
+      <c r="O56">
+        <f t="shared" si="4"/>
+        <v>509.57842816655625</v>
+      </c>
+      <c r="P56">
+        <f t="shared" si="5"/>
+        <v>700.82842816655625</v>
+      </c>
+      <c r="Q56">
+        <f t="shared" si="6"/>
+        <v>137.5590436741528</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>15</v>
       </c>
@@ -13675,8 +15205,24 @@
       <c r="M57" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N57">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O57">
+        <f t="shared" si="4"/>
+        <v>676.55330281229556</v>
+      </c>
+      <c r="P57">
+        <f t="shared" si="5"/>
+        <v>676.55330281229556</v>
+      </c>
+      <c r="Q57">
+        <f t="shared" si="6"/>
+        <v>163.31661943172617</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>15</v>
       </c>
@@ -13719,8 +15265,24 @@
       <c r="M58" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N58">
+        <f t="shared" si="3"/>
+        <v>686.62161180146677</v>
+      </c>
+      <c r="O58">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P58">
+        <f t="shared" si="5"/>
+        <v>686.62161180146677</v>
+      </c>
+      <c r="Q58">
+        <f t="shared" si="6"/>
+        <v>171.84070925078197</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>15</v>
       </c>
@@ -13763,8 +15325,24 @@
       <c r="M59" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N59">
+        <f t="shared" si="3"/>
+        <v>679.70350991933572</v>
+      </c>
+      <c r="O59">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P59">
+        <f t="shared" si="5"/>
+        <v>679.70350991933572</v>
+      </c>
+      <c r="Q59">
+        <f t="shared" si="6"/>
+        <v>171.84070925078186</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>15</v>
       </c>
@@ -13807,8 +15385,24 @@
       <c r="M60" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N60">
+        <f t="shared" si="3"/>
+        <v>689.7100501417043</v>
+      </c>
+      <c r="O60">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P60">
+        <f t="shared" si="5"/>
+        <v>689.7100501417043</v>
+      </c>
+      <c r="Q60">
+        <f t="shared" si="6"/>
+        <v>171.9642467843895</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>15</v>
       </c>
@@ -13851,8 +15445,24 @@
       <c r="M61" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N61">
+        <f t="shared" si="3"/>
+        <v>661.32730179492683</v>
+      </c>
+      <c r="O61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P61">
+        <f t="shared" si="5"/>
+        <v>661.32730179492683</v>
+      </c>
+      <c r="Q61">
+        <f t="shared" si="6"/>
+        <v>163.25485066492342</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>15</v>
       </c>
@@ -13895,8 +15505,24 @@
       <c r="M62" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N62">
+        <f t="shared" si="3"/>
+        <v>616.25</v>
+      </c>
+      <c r="O62">
+        <f t="shared" si="4"/>
+        <v>89.427276360729323</v>
+      </c>
+      <c r="P62">
+        <f t="shared" si="5"/>
+        <v>705.67727636072937</v>
+      </c>
+      <c r="Q62">
+        <f t="shared" si="6"/>
+        <v>184.84303466317715</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>15</v>
       </c>
@@ -13939,8 +15565,24 @@
       <c r="M63" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N63">
+        <f t="shared" si="3"/>
+        <v>531.25</v>
+      </c>
+      <c r="O63">
+        <f t="shared" si="4"/>
+        <v>219.08609476055415</v>
+      </c>
+      <c r="P63">
+        <f t="shared" si="5"/>
+        <v>750.33609476055415</v>
+      </c>
+      <c r="Q63">
+        <f t="shared" si="6"/>
+        <v>201.9529830680915</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>15</v>
       </c>
@@ -13983,8 +15625,24 @@
       <c r="M64" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N64">
+        <f t="shared" si="3"/>
+        <v>446.25</v>
+      </c>
+      <c r="O64">
+        <f t="shared" si="4"/>
+        <v>296.92091781120558</v>
+      </c>
+      <c r="P64">
+        <f t="shared" si="5"/>
+        <v>743.17091781120553</v>
+      </c>
+      <c r="Q64">
+        <f t="shared" si="6"/>
+        <v>223.41762953273576</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>15</v>
       </c>
@@ -14027,8 +15685,24 @@
       <c r="M65" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N65">
+        <f t="shared" si="3"/>
+        <v>361.25</v>
+      </c>
+      <c r="O65">
+        <f t="shared" si="4"/>
+        <v>619.63801685923909</v>
+      </c>
+      <c r="P65">
+        <f t="shared" si="5"/>
+        <v>980.88801685923909</v>
+      </c>
+      <c r="Q65">
+        <f t="shared" si="6"/>
+        <v>171.90247801758665</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>15</v>
       </c>
@@ -14071,8 +15745,24 @@
       <c r="M66" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N66">
+        <f t="shared" si="3"/>
+        <v>276.25</v>
+      </c>
+      <c r="O66">
+        <f t="shared" si="4"/>
+        <v>671.90057045272749</v>
+      </c>
+      <c r="P66">
+        <f t="shared" si="5"/>
+        <v>948.15057045272749</v>
+      </c>
+      <c r="Q66">
+        <f t="shared" si="6"/>
+        <v>184.78126589637452</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>15</v>
       </c>
@@ -14115,8 +15805,24 @@
       <c r="M67" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N67">
+        <f t="shared" si="3"/>
+        <v>191.25</v>
+      </c>
+      <c r="O67">
+        <f t="shared" si="4"/>
+        <v>797.01938449240572</v>
+      </c>
+      <c r="P67">
+        <f t="shared" si="5"/>
+        <v>988.26938449240572</v>
+      </c>
+      <c r="Q67">
+        <f t="shared" si="6"/>
+        <v>158.7148463047746</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>15</v>
       </c>
@@ -14145,22 +15851,38 @@
         <v>54.671898844560701</v>
       </c>
       <c r="J68">
-        <f t="shared" ref="J68:J90" si="3">E68*MIN(G68,I68)</f>
+        <f t="shared" ref="J68:J91" si="7">E68*MIN(G68,I68)</f>
         <v>0</v>
       </c>
       <c r="K68">
-        <f t="shared" ref="K68:K90" si="4">F68*MAX(0,I68-G68)</f>
+        <f t="shared" ref="K68:K91" si="8">F68*MAX(0,I68-G68)</f>
         <v>1161.777850446915</v>
       </c>
       <c r="L68">
-        <f t="shared" ref="L68:L90" si="5">J68+K68</f>
+        <f t="shared" ref="L68:L91" si="9">J68+K68</f>
         <v>1161.777850446915</v>
       </c>
       <c r="M68" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N68">
+        <f t="shared" ref="N68" si="10">E68*MIN(G68,H68)</f>
+        <v>0</v>
+      </c>
+      <c r="O68">
+        <f t="shared" ref="O68" si="11">F68*MAX(0,H68-G68)</f>
+        <v>985.58244313639887</v>
+      </c>
+      <c r="P68">
+        <f t="shared" ref="P68" si="12">N68+O68</f>
+        <v>985.58244313639887</v>
+      </c>
+      <c r="Q68">
+        <f t="shared" ref="Q68:Q91" si="13">L68-P68</f>
+        <v>176.19540731051609</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>15</v>
       </c>
@@ -14182,29 +15904,28 @@
       <c r="G69">
         <v>45</v>
       </c>
-      <c r="H69">
-        <v>47.269286065260502</v>
-      </c>
-      <c r="I69">
-        <v>53.131813135816799</v>
+      <c r="I69" s="4">
+        <v>75.787299134246894</v>
       </c>
       <c r="J69">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>999</v>
       </c>
       <c r="K69">
-        <f t="shared" si="4"/>
-        <v>166.70216928424438</v>
+        <f t="shared" si="8"/>
+        <v>631.13963225206135</v>
       </c>
       <c r="L69">
-        <f t="shared" si="5"/>
-        <v>1165.7021692842443</v>
+        <f t="shared" si="9"/>
+        <v>1630.1396322520613</v>
       </c>
       <c r="M69" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N69" s="4"/>
+      <c r="O69" s="4"/>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>15</v>
       </c>
@@ -14226,29 +15947,28 @@
       <c r="G70">
         <v>41</v>
       </c>
-      <c r="H70">
-        <v>44.697810697191898</v>
-      </c>
-      <c r="I70">
-        <v>51.355256692569398</v>
+      <c r="I70" s="4">
+        <v>64.409505937268307</v>
       </c>
       <c r="J70">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>910.19999999999993</v>
       </c>
       <c r="K70">
-        <f t="shared" si="4"/>
-        <v>212.28276219767267</v>
+        <f t="shared" si="8"/>
+        <v>479.89487171400026</v>
       </c>
       <c r="L70">
-        <f t="shared" si="5"/>
-        <v>1122.4827621976726</v>
+        <f t="shared" si="9"/>
+        <v>1390.0948717140002</v>
       </c>
       <c r="M70" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N70" s="4"/>
+      <c r="O70" s="4"/>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>15</v>
       </c>
@@ -14270,29 +15990,28 @@
       <c r="G71">
         <v>37</v>
       </c>
-      <c r="H71">
-        <v>46.5704562412418</v>
-      </c>
-      <c r="I71">
-        <v>54.046843436641197</v>
+      <c r="I71" s="4">
+        <v>63.558339772601798</v>
       </c>
       <c r="J71">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>821.4</v>
       </c>
       <c r="K71">
-        <f t="shared" si="4"/>
-        <v>349.46029045114454</v>
+        <f t="shared" si="8"/>
+        <v>544.4459653383368</v>
       </c>
       <c r="L71">
-        <f t="shared" si="5"/>
-        <v>1170.8602904511445</v>
+        <f t="shared" si="9"/>
+        <v>1365.8459653383368</v>
       </c>
       <c r="M71" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N71" s="4"/>
+      <c r="O71" s="4"/>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>15</v>
       </c>
@@ -14314,29 +16033,28 @@
       <c r="G72">
         <v>33</v>
       </c>
-      <c r="H72">
-        <v>43.796975377167897</v>
-      </c>
-      <c r="I72">
-        <v>51.681741250978099</v>
+      <c r="I72" s="4">
+        <v>62.285730055351401</v>
       </c>
       <c r="J72">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>732.6</v>
       </c>
       <c r="K72">
-        <f t="shared" si="4"/>
-        <v>382.97569564505102</v>
+        <f t="shared" si="8"/>
+        <v>600.35746613470371</v>
       </c>
       <c r="L72">
-        <f t="shared" si="5"/>
-        <v>1115.5756956450509</v>
+        <f t="shared" si="9"/>
+        <v>1332.9574661347037</v>
       </c>
       <c r="M72" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N72" s="4"/>
+      <c r="O72" s="4"/>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>15</v>
       </c>
@@ -14358,29 +16076,28 @@
       <c r="G73">
         <v>29</v>
       </c>
-      <c r="H73">
-        <v>43.0457333163478</v>
-      </c>
-      <c r="I73">
-        <v>50.109374146936197</v>
+      <c r="I73" s="4">
+        <v>57.854856259757398</v>
       </c>
       <c r="J73">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>643.79999999999995</v>
       </c>
       <c r="K73">
-        <f t="shared" si="4"/>
-        <v>432.74217001219205</v>
+        <f t="shared" si="8"/>
+        <v>591.52455332502666</v>
       </c>
       <c r="L73">
-        <f t="shared" si="5"/>
-        <v>1076.5421700121919</v>
+        <f t="shared" si="9"/>
+        <v>1235.3245533250265</v>
       </c>
       <c r="M73" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N73" s="4"/>
+      <c r="O73" s="4"/>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>15</v>
       </c>
@@ -14402,29 +16119,28 @@
       <c r="G74">
         <v>25</v>
       </c>
-      <c r="H74">
-        <v>40.267884765873802</v>
-      </c>
-      <c r="I74">
-        <v>46.727692951645999</v>
+      <c r="I74" s="4">
+        <v>59.319855550123698</v>
       </c>
       <c r="J74">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>555</v>
       </c>
       <c r="K74">
-        <f t="shared" si="4"/>
-        <v>445.41770550874298</v>
+        <f t="shared" si="8"/>
+        <v>703.55703877753581</v>
       </c>
       <c r="L74">
-        <f t="shared" si="5"/>
-        <v>1000.417705508743</v>
+        <f t="shared" si="9"/>
+        <v>1258.5570387775358</v>
       </c>
       <c r="M74" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N74" s="4"/>
+      <c r="O74" s="4"/>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>15</v>
       </c>
@@ -14446,29 +16162,28 @@
       <c r="G75">
         <v>21</v>
       </c>
-      <c r="H75">
-        <v>38.5109829114269</v>
-      </c>
-      <c r="I75">
-        <v>45.589910644415703</v>
+      <c r="I75" s="4">
+        <v>55.098717928500399</v>
       </c>
       <c r="J75">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>466.2</v>
       </c>
       <c r="K75">
-        <f t="shared" si="4"/>
-        <v>504.09316821052192</v>
+        <f t="shared" si="8"/>
+        <v>699.02371753425814</v>
       </c>
       <c r="L75">
-        <f t="shared" si="5"/>
-        <v>970.29316821052191</v>
+        <f t="shared" si="9"/>
+        <v>1165.2237175342582</v>
       </c>
       <c r="M75" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N75" s="4"/>
+      <c r="O75" s="4"/>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>15</v>
       </c>
@@ -14490,29 +16205,28 @@
       <c r="G76">
         <v>17</v>
       </c>
-      <c r="H76">
-        <v>34.523285228120599</v>
-      </c>
-      <c r="I76">
-        <v>43.018435276347098</v>
+      <c r="I76" s="4">
+        <v>52.984009587939298</v>
       </c>
       <c r="J76">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>377.4</v>
       </c>
       <c r="K76">
-        <f t="shared" si="4"/>
-        <v>533.37792316511548</v>
+        <f t="shared" si="8"/>
+        <v>737.67219655275562</v>
       </c>
       <c r="L76">
-        <f t="shared" si="5"/>
-        <v>910.77792316511545</v>
+        <f t="shared" si="9"/>
+        <v>1115.0721965527555</v>
       </c>
       <c r="M76" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N76" s="4"/>
+      <c r="O76" s="4"/>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>15</v>
       </c>
@@ -14534,29 +16248,28 @@
       <c r="G77">
         <v>13</v>
       </c>
-      <c r="H77">
-        <v>33.365848332089698</v>
-      </c>
-      <c r="I77">
-        <v>41.055160239494697</v>
+      <c r="I77" s="4">
+        <v>51.291533281819099</v>
       </c>
       <c r="J77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>288.59999999999997</v>
       </c>
       <c r="K77">
-        <f t="shared" si="4"/>
-        <v>575.13078490964131</v>
+        <f t="shared" si="8"/>
+        <v>784.97643227729156</v>
       </c>
       <c r="L77">
-        <f t="shared" si="5"/>
-        <v>863.73078490964122</v>
+        <f t="shared" si="9"/>
+        <v>1073.5764322772916</v>
       </c>
       <c r="M77" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N77" s="4"/>
+      <c r="O77" s="4"/>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>15</v>
       </c>
@@ -14578,29 +16291,28 @@
       <c r="G78">
         <v>9</v>
       </c>
-      <c r="H78">
-        <v>33.016433420080403</v>
-      </c>
-      <c r="I78">
-        <v>39.691350161058402</v>
+      <c r="I78" s="4">
+        <v>50.228265497610799</v>
       </c>
       <c r="J78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>199.79999999999998</v>
       </c>
       <c r="K78">
-        <f t="shared" si="4"/>
-        <v>629.17267830169726</v>
+        <f t="shared" si="8"/>
+        <v>845.17944270102134</v>
       </c>
       <c r="L78">
-        <f t="shared" si="5"/>
-        <v>828.97267830169721</v>
+        <f t="shared" si="9"/>
+        <v>1044.9794427010213</v>
       </c>
       <c r="M78" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N78" s="4"/>
+      <c r="O78" s="4"/>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>15</v>
       </c>
@@ -14608,10 +16320,10 @@
         <v>19</v>
       </c>
       <c r="C79" s="1">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D79" s="1">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E79" s="1">
         <v>20.5</v>
@@ -14622,29 +16334,28 @@
       <c r="G79">
         <v>0</v>
       </c>
-      <c r="H79">
-        <v>32.058818176854899</v>
-      </c>
-      <c r="I79">
-        <v>39.333199876248898</v>
+      <c r="I79" s="4">
+        <v>48.746708088246798</v>
       </c>
       <c r="J79">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="J79" si="14">E79*MIN(G79,I79)</f>
         <v>0</v>
       </c>
       <c r="K79">
-        <f t="shared" si="4"/>
-        <v>873.19703725272552</v>
+        <f t="shared" ref="K79" si="15">F79*MAX(0,I79-G79)</f>
+        <v>1082.1769195590789</v>
       </c>
       <c r="L79">
-        <f t="shared" si="5"/>
-        <v>873.19703725272552</v>
+        <f t="shared" ref="L79" si="16">J79+K79</f>
+        <v>1082.1769195590789</v>
       </c>
       <c r="M79" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N79" s="4"/>
+      <c r="O79" s="4"/>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>15</v>
       </c>
@@ -14664,31 +16375,30 @@
         <v>22.2</v>
       </c>
       <c r="G80">
-        <v>45</v>
-      </c>
-      <c r="H80">
-        <v>32.515241405666998</v>
-      </c>
-      <c r="I80">
-        <v>40.597645089082597</v>
+        <v>49</v>
+      </c>
+      <c r="I80" s="4">
+        <v>48.746708088246798</v>
       </c>
       <c r="J80">
-        <f t="shared" si="3"/>
-        <v>832.2517243261932</v>
+        <f t="shared" si="7"/>
+        <v>999.3075158090594</v>
       </c>
       <c r="K80">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L80">
-        <f t="shared" si="5"/>
-        <v>832.2517243261932</v>
+        <f t="shared" si="9"/>
+        <v>999.3075158090594</v>
       </c>
       <c r="M80" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+      <c r="N80" s="4"/>
+      <c r="O80" s="4"/>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>15</v>
       </c>
@@ -14708,31 +16418,30 @@
         <v>22.2</v>
       </c>
       <c r="G81">
-        <v>41</v>
-      </c>
-      <c r="H81">
-        <v>31.970372527252501</v>
-      </c>
-      <c r="I81">
-        <v>40.048408524267899</v>
+        <v>45</v>
+      </c>
+      <c r="I81" s="4">
+        <v>49.577767965559097</v>
       </c>
       <c r="J81">
-        <f t="shared" si="3"/>
-        <v>820.99237474749191</v>
+        <f t="shared" si="7"/>
+        <v>922.5</v>
       </c>
       <c r="K81">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>101.62644883541195</v>
       </c>
       <c r="L81">
-        <f t="shared" si="5"/>
-        <v>820.99237474749191</v>
+        <f t="shared" si="9"/>
+        <v>1024.126448835412</v>
       </c>
       <c r="M81" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+      <c r="N81" s="4"/>
+      <c r="O81" s="4"/>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>15</v>
       </c>
@@ -14752,31 +16461,30 @@
         <v>22.2</v>
       </c>
       <c r="G82">
+        <v>41</v>
+      </c>
+      <c r="I82" s="4">
+        <v>46.200700171888997</v>
+      </c>
+      <c r="J82">
+        <f t="shared" si="7"/>
+        <v>840.5</v>
+      </c>
+      <c r="K82">
+        <f t="shared" si="8"/>
+        <v>115.45554381593573</v>
+      </c>
+      <c r="L82">
+        <f t="shared" si="9"/>
+        <v>955.9555438159357</v>
+      </c>
+      <c r="M82" t="s">
         <v>37</v>
       </c>
-      <c r="H82">
-        <v>31.8185954248484</v>
-      </c>
-      <c r="I82">
-        <v>40.507015596280198</v>
-      </c>
-      <c r="J82">
-        <f t="shared" si="3"/>
-        <v>758.5</v>
-      </c>
-      <c r="K82">
-        <f t="shared" si="4"/>
-        <v>77.855746237420391</v>
-      </c>
-      <c r="L82">
-        <f t="shared" si="5"/>
-        <v>836.35574623742036</v>
-      </c>
-      <c r="M82" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N82" s="4"/>
+      <c r="O82" s="4"/>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>15</v>
       </c>
@@ -14796,31 +16504,30 @@
         <v>22.2</v>
       </c>
       <c r="G83">
-        <v>33</v>
-      </c>
-      <c r="H83">
-        <v>31.269358860033801</v>
-      </c>
-      <c r="I83">
-        <v>39.349578700249303</v>
+        <v>37</v>
+      </c>
+      <c r="I83" s="4">
+        <v>46.821629634302099</v>
       </c>
       <c r="J83">
-        <f t="shared" si="3"/>
-        <v>676.5</v>
+        <f t="shared" si="7"/>
+        <v>758.5</v>
       </c>
       <c r="K83">
-        <f t="shared" si="4"/>
-        <v>140.96064714553452</v>
+        <f t="shared" si="8"/>
+        <v>218.04017788150659</v>
       </c>
       <c r="L83">
-        <f t="shared" si="5"/>
-        <v>817.46064714553449</v>
+        <f t="shared" si="9"/>
+        <v>976.54017788150657</v>
       </c>
       <c r="M83" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+      <c r="N83" s="4"/>
+      <c r="O83" s="4"/>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>15</v>
       </c>
@@ -14840,31 +16547,30 @@
         <v>22.2</v>
       </c>
       <c r="G84">
-        <v>29</v>
-      </c>
-      <c r="H84">
-        <v>33.341826056889097</v>
-      </c>
-      <c r="I84">
-        <v>41.836976105115603</v>
+        <v>33</v>
+      </c>
+      <c r="I84" s="4">
+        <v>48.286628924668399</v>
       </c>
       <c r="J84">
-        <f t="shared" si="3"/>
-        <v>594.5</v>
+        <f t="shared" si="7"/>
+        <v>676.5</v>
       </c>
       <c r="K84">
-        <f t="shared" si="4"/>
-        <v>284.98086953356636</v>
+        <f t="shared" si="8"/>
+        <v>339.36316212763847</v>
       </c>
       <c r="L84">
-        <f t="shared" si="5"/>
-        <v>879.48086953356642</v>
+        <f t="shared" si="9"/>
+        <v>1015.8631621276385</v>
       </c>
       <c r="M84" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+      <c r="N84" s="4"/>
+      <c r="O84" s="4"/>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>15</v>
       </c>
@@ -14884,31 +16590,30 @@
         <v>22.2</v>
       </c>
       <c r="G85">
-        <v>25</v>
-      </c>
-      <c r="H85">
-        <v>35.418660940144498</v>
-      </c>
-      <c r="I85">
-        <v>44.5198274763871</v>
+        <v>29</v>
+      </c>
+      <c r="I85" s="4">
+        <v>48.908741109867002</v>
       </c>
       <c r="J85">
-        <f t="shared" si="3"/>
-        <v>512.5</v>
+        <f t="shared" si="7"/>
+        <v>594.5</v>
       </c>
       <c r="K85">
-        <f t="shared" si="4"/>
-        <v>433.34016997579363</v>
+        <f t="shared" si="8"/>
+        <v>441.97405263904744</v>
       </c>
       <c r="L85">
-        <f t="shared" si="5"/>
-        <v>945.84016997579363</v>
+        <f t="shared" si="9"/>
+        <v>1036.4740526390474</v>
       </c>
       <c r="M85" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+      <c r="N85" s="4"/>
+      <c r="O85" s="4"/>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>15</v>
       </c>
@@ -14928,31 +16633,30 @@
         <v>22.2</v>
       </c>
       <c r="G86">
-        <v>21</v>
-      </c>
-      <c r="H86">
-        <v>34.463229540119002</v>
-      </c>
-      <c r="I86">
-        <v>45.5800833500154</v>
+        <v>25</v>
+      </c>
+      <c r="I86" s="4">
+        <v>66.5845331398924</v>
       </c>
       <c r="J86">
-        <f t="shared" si="3"/>
-        <v>430.5</v>
+        <f t="shared" si="7"/>
+        <v>512.5</v>
       </c>
       <c r="K86">
-        <f t="shared" si="4"/>
-        <v>545.67785037034184</v>
+        <f t="shared" si="8"/>
+        <v>923.17663570561126</v>
       </c>
       <c r="L86">
-        <f t="shared" si="5"/>
-        <v>976.17785037034184</v>
+        <f t="shared" si="9"/>
+        <v>1435.6766357056113</v>
       </c>
       <c r="M86" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+      <c r="N86" s="4"/>
+      <c r="O86" s="4"/>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>15</v>
       </c>
@@ -14972,31 +16676,30 @@
         <v>22.2</v>
       </c>
       <c r="G87">
-        <v>17</v>
-      </c>
-      <c r="H87">
-        <v>46.436149884438201</v>
-      </c>
-      <c r="I87">
-        <v>54.123277948643299</v>
+        <v>21</v>
+      </c>
+      <c r="I87" s="4">
+        <v>68.890842571712398</v>
       </c>
       <c r="J87">
-        <f t="shared" si="3"/>
-        <v>348.5</v>
+        <f t="shared" si="7"/>
+        <v>430.5</v>
       </c>
       <c r="K87">
-        <f t="shared" si="4"/>
-        <v>824.13677045988118</v>
+        <f t="shared" si="8"/>
+        <v>1063.1767050920153</v>
       </c>
       <c r="L87">
-        <f t="shared" si="5"/>
-        <v>1172.6367704598811</v>
+        <f t="shared" si="9"/>
+        <v>1493.6767050920153</v>
       </c>
       <c r="M87" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+      <c r="N87" s="4"/>
+      <c r="O87" s="4"/>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>15</v>
       </c>
@@ -15016,31 +16719,30 @@
         <v>22.2</v>
       </c>
       <c r="G88">
-        <v>13</v>
-      </c>
-      <c r="H88">
-        <v>44.874701996396603</v>
-      </c>
-      <c r="I88">
-        <v>53.365484358223</v>
+        <v>17</v>
+      </c>
+      <c r="I88" s="4">
+        <v>73.092662387838402</v>
       </c>
       <c r="J88">
-        <f t="shared" si="3"/>
-        <v>266.5</v>
+        <f t="shared" si="7"/>
+        <v>348.5</v>
       </c>
       <c r="K88">
-        <f t="shared" si="4"/>
-        <v>896.11375275255057</v>
+        <f t="shared" si="8"/>
+        <v>1245.2571050100125</v>
       </c>
       <c r="L88">
-        <f t="shared" si="5"/>
-        <v>1162.6137527525507</v>
+        <f t="shared" si="9"/>
+        <v>1593.7571050100125</v>
       </c>
       <c r="M88" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+      <c r="N88" s="4"/>
+      <c r="O88" s="4"/>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>15</v>
       </c>
@@ -15060,31 +16762,30 @@
         <v>22.2</v>
       </c>
       <c r="G89">
-        <v>9</v>
-      </c>
-      <c r="H89">
-        <v>46.3411527052357</v>
-      </c>
-      <c r="I89">
-        <v>53.615534404629699</v>
+        <v>13</v>
+      </c>
+      <c r="I89" s="4">
+        <v>76.871855928594996</v>
       </c>
       <c r="J89">
-        <f t="shared" si="3"/>
-        <v>184.5</v>
+        <f t="shared" si="7"/>
+        <v>266.5</v>
       </c>
       <c r="K89">
-        <f t="shared" si="4"/>
-        <v>990.46486378277928</v>
+        <f t="shared" si="8"/>
+        <v>1417.9552016148089</v>
       </c>
       <c r="L89">
-        <f t="shared" si="5"/>
-        <v>1174.9648637827793</v>
+        <f t="shared" si="9"/>
+        <v>1684.4552016148089</v>
       </c>
       <c r="M89" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+      <c r="N89" s="4"/>
+      <c r="O89" s="4"/>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>15</v>
       </c>
@@ -15104,32 +16805,1353 @@
         <v>22.2</v>
       </c>
       <c r="G90">
-        <v>0</v>
-      </c>
-      <c r="H90">
-        <v>46.801943620448</v>
-      </c>
-      <c r="I90">
-        <v>55.097272015869201</v>
+        <v>9</v>
+      </c>
+      <c r="I90" s="4">
+        <v>81.283411918691698</v>
       </c>
       <c r="J90">
+        <f t="shared" si="7"/>
+        <v>184.5</v>
+      </c>
+      <c r="K90">
+        <f t="shared" si="8"/>
+        <v>1604.6917445949557</v>
+      </c>
+      <c r="L90">
+        <f t="shared" si="9"/>
+        <v>1789.1917445949557</v>
+      </c>
+      <c r="M90" t="s">
+        <v>45</v>
+      </c>
+      <c r="N90" s="4"/>
+      <c r="O90" s="4"/>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>15</v>
+      </c>
+      <c r="B91" t="s">
+        <v>19</v>
+      </c>
+      <c r="C91" s="1">
+        <v>16</v>
+      </c>
+      <c r="D91" s="1">
+        <v>8</v>
+      </c>
+      <c r="E91" s="1">
+        <v>20.5</v>
+      </c>
+      <c r="F91" s="1">
+        <v>22.2</v>
+      </c>
+      <c r="G91">
+        <v>0</v>
+      </c>
+      <c r="I91" s="4">
+        <v>79.590935612571499</v>
+      </c>
+      <c r="J91">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K91">
+        <f t="shared" si="8"/>
+        <v>1766.9187705990873</v>
+      </c>
+      <c r="L91">
+        <f t="shared" si="9"/>
+        <v>1766.9187705990873</v>
+      </c>
+      <c r="M91" t="s">
+        <v>46</v>
+      </c>
+      <c r="N91" s="4"/>
+      <c r="O91" s="4"/>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="D92" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A56BD598-88B9-4FBE-A43A-FDC6C084D6A3}">
+  <dimension ref="A1:J67"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2">
+        <v>0.41868386608424402</v>
+      </c>
+      <c r="D2">
+        <v>0.98875624871871604</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="str">
+        <f>A2</f>
+        <v>A</v>
+      </c>
+      <c r="B3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3">
+        <v>45.0506993834071</v>
+      </c>
+      <c r="D3">
+        <v>0.99082995600271195</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="str">
+        <f>A3</f>
+        <v>A</v>
+      </c>
+      <c r="B4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4">
+        <v>75.787299134246894</v>
+      </c>
+      <c r="D4">
+        <v>0.98967877249144398</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5">
+        <v>0.19869742797218401</v>
+      </c>
+      <c r="D5">
+        <v>0.94382066768643602</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H5" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5" t="s">
+        <v>51</v>
+      </c>
+      <c r="J5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" t="str">
+        <f t="shared" ref="A6:A37" si="0">A5</f>
+        <v>b</v>
+      </c>
+      <c r="B6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6">
+        <v>41.462318452052401</v>
+      </c>
+      <c r="D6">
+        <v>0.94602053206755699</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.41868386608424402</v>
+      </c>
+      <c r="I6" s="4">
+        <v>45.0506993834071</v>
+      </c>
+      <c r="J6" s="4">
+        <v>75.787299134246894</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" t="str">
+        <f t="shared" si="0"/>
+        <v>b</v>
+      </c>
+      <c r="B7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7">
+        <v>64.409505937268307</v>
+      </c>
+      <c r="D7">
+        <v>0.94516108684339095</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.19869742797218401</v>
+      </c>
+      <c r="I7" s="4">
+        <v>41.462318452052401</v>
+      </c>
+      <c r="J7" s="4">
+        <v>64.409505937268307</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8">
+        <v>0.189235645687794</v>
+      </c>
+      <c r="D8">
+        <v>0.89887720183558495</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.189235645687794</v>
+      </c>
+      <c r="I8" s="4">
+        <v>37.4528882090423</v>
+      </c>
+      <c r="J8" s="4">
+        <v>63.558339772601798</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" t="str">
+        <f t="shared" ref="A9:A40" si="1">A8</f>
+        <v>c</v>
+      </c>
+      <c r="B9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9">
+        <v>37.4528882090423</v>
+      </c>
+      <c r="D9">
+        <v>0.90122687776954202</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.17937962247488601</v>
+      </c>
+      <c r="I9" s="4">
+        <v>33.442669484175099</v>
+      </c>
+      <c r="J9" s="4">
+        <v>62.285730055351401</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="str">
+        <f t="shared" si="1"/>
+        <v>c</v>
+      </c>
+      <c r="B10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10">
+        <v>63.558339772601798</v>
+      </c>
+      <c r="D10">
+        <v>0.90212180467727399</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.38162521880371902</v>
+      </c>
+      <c r="I10" s="4">
+        <v>29.644552378849699</v>
+      </c>
+      <c r="J10" s="4">
+        <v>57.854856259757398</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11">
+        <v>0.17937962247488601</v>
+      </c>
+      <c r="D11">
+        <v>0.852061091574282</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.37176919559081101</v>
+      </c>
+      <c r="I11" s="4">
+        <v>25.003548168356598</v>
+      </c>
+      <c r="J11" s="4">
+        <v>59.319855550123698</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" t="str">
+        <f t="shared" ref="A12:A43" si="2">A11</f>
+        <v>d</v>
+      </c>
+      <c r="B12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12">
+        <v>33.442669484175099</v>
+      </c>
+      <c r="D12">
+        <v>0.85268793465062298</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.151388516550234</v>
+      </c>
+      <c r="I12" s="4">
+        <v>21.4147729960733</v>
+      </c>
+      <c r="J12" s="4">
+        <v>55.098717928500399</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" t="str">
+        <f t="shared" si="2"/>
+        <v>d</v>
+      </c>
+      <c r="B13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13">
+        <v>62.285730055351401</v>
+      </c>
+      <c r="D13">
+        <v>0.85722564773784504</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.35284563102203398</v>
+      </c>
+      <c r="I13" s="4">
+        <v>18.037705202403199</v>
+      </c>
+      <c r="J13" s="4">
+        <v>52.984009587939298</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14">
+        <v>0.38162521880371902</v>
+      </c>
+      <c r="D14">
+        <v>0.81272767413621705</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.13325343383848601</v>
+      </c>
+      <c r="I14" s="4">
+        <v>13.3970952328386</v>
+      </c>
+      <c r="J14" s="4">
+        <v>51.291533281819099</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" t="str">
+        <f t="shared" ref="A15:A46" si="3">A14</f>
+        <v>e</v>
+      </c>
+      <c r="B15" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15">
+        <v>29.644552378849699</v>
+      </c>
+      <c r="D15">
+        <v>0.81163168435494204</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.124185892482614</v>
+      </c>
+      <c r="I15" s="4">
+        <v>9.3864822670430303</v>
+      </c>
+      <c r="J15" s="4">
+        <v>50.228265497610799</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" t="str">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K90">
+        <v>e</v>
+      </c>
+      <c r="B16" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16">
+        <v>57.854856259757398</v>
+      </c>
+      <c r="D16">
+        <v>0.81057511866651899</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H16" s="4">
+        <v>-9.6194786557962403E-2</v>
+      </c>
+      <c r="I16" s="4">
+        <v>48.744342642675697</v>
+      </c>
+      <c r="J16" s="4">
+        <v>48.746708088246798</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17">
+        <v>0.37176919559081101</v>
+      </c>
+      <c r="D17">
+        <v>0.76591156387491499</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.105262327913834</v>
+      </c>
+      <c r="I17" s="4">
+        <v>45.789112642517999</v>
+      </c>
+      <c r="J17" s="4">
+        <v>49.577767965559097</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" t="str">
+        <f t="shared" ref="A18:A49" si="4">A17</f>
+        <v>f</v>
+      </c>
+      <c r="B18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18">
+        <v>25.003548168356598</v>
+      </c>
+      <c r="D18">
+        <v>0.76686168451263903</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H18" s="4">
+        <v>0.30553671960008399</v>
+      </c>
+      <c r="I18" s="4">
+        <v>41.5695519846088</v>
+      </c>
+      <c r="J18" s="4">
+        <v>46.200700171888997</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" t="str">
         <f t="shared" si="4"/>
-        <v>1223.1594387522962</v>
-      </c>
-      <c r="L90">
+        <v>f</v>
+      </c>
+      <c r="B19" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19">
+        <v>59.319855550123698</v>
+      </c>
+      <c r="D19">
+        <v>0.76932174790658003</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H19" s="4">
+        <v>-0.124974374339647</v>
+      </c>
+      <c r="I19" s="4">
+        <v>37.558544777884599</v>
+      </c>
+      <c r="J19" s="4">
+        <v>46.821629634302099</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" t="s">
+        <v>50</v>
+      </c>
+      <c r="C20">
+        <v>0.151388516550234</v>
+      </c>
+      <c r="D20">
+        <v>0.71910333843218199</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H20" s="4">
+        <v>0.28661315503130402</v>
+      </c>
+      <c r="I20" s="4">
+        <v>33.340166842760901</v>
+      </c>
+      <c r="J20" s="4">
+        <v>48.286628924668399</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" t="str">
+        <f t="shared" ref="A21:A67" si="5">A20</f>
+        <v>g</v>
+      </c>
+      <c r="B21" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21">
+        <v>21.4147729960733</v>
+      </c>
+      <c r="D21">
+        <v>0.72017961616703197</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H21" s="4">
+        <v>6.7415198776274096E-2</v>
+      </c>
+      <c r="I21" s="4">
+        <v>29.752180152334599</v>
+      </c>
+      <c r="J21" s="4">
+        <v>48.908741109867002</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" t="str">
         <f t="shared" si="5"/>
-        <v>1223.1594387522962</v>
-      </c>
-      <c r="M90" t="s">
+        <v>g</v>
+      </c>
+      <c r="B22" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22">
+        <v>55.098717928500399</v>
+      </c>
+      <c r="D22">
+        <v>0.71891804519577995</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H22" s="4">
+        <v>-0.15257123933578101</v>
+      </c>
+      <c r="I22" s="4">
+        <v>25.5322252534969</v>
+      </c>
+      <c r="J22" s="4">
+        <v>66.5845331398924</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23">
+        <v>0.35284563102203398</v>
+      </c>
+      <c r="D23">
+        <v>0.67602463217321296</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H23" s="4">
+        <v>-0.162033021620171</v>
+      </c>
+      <c r="I23" s="4">
+        <v>21.7321369435289</v>
+      </c>
+      <c r="J23" s="4">
+        <v>68.890842571712398</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" t="str">
+        <f t="shared" ref="A24:A67" si="6">A23</f>
+        <v>h</v>
+      </c>
+      <c r="B24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24">
+        <v>18.037705202403199</v>
+      </c>
+      <c r="D24">
+        <v>0.67910759623421002</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H24" s="4">
+        <v>-0.17149480390456101</v>
+      </c>
+      <c r="I24" s="4">
+        <v>17.934019838203501</v>
+      </c>
+      <c r="J24" s="4">
+        <v>73.092662387838402</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" t="str">
+        <f t="shared" si="6"/>
+        <v>h</v>
+      </c>
+      <c r="B25" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25">
+        <v>52.984009587939298</v>
+      </c>
+      <c r="D25">
+        <v>0.67405342753063202</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H25" s="4">
+        <v>-0.18056234526043699</v>
+      </c>
+      <c r="I25" s="4">
+        <v>13.503540283537999</v>
+      </c>
+      <c r="J25" s="4">
+        <v>76.871855928594996</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26">
+        <v>0.13325343383848601</v>
+      </c>
+      <c r="D26">
+        <v>0.63296169555138504</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H26" s="4">
+        <v>2.0500528282841601E-2</v>
+      </c>
+      <c r="I26" s="4">
+        <v>9.4937157995994408</v>
+      </c>
+      <c r="J26" s="4">
+        <v>81.283411918691698</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" t="str">
+        <f t="shared" ref="A27:A67" si="7">A26</f>
+        <v>i</v>
+      </c>
+      <c r="B27" t="s">
+        <v>51</v>
+      </c>
+      <c r="C27">
+        <v>13.3970952328386</v>
+      </c>
+      <c r="D27">
+        <v>0.636210240802359</v>
+      </c>
+      <c r="G27" s="3" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="D91" s="1"/>
+      <c r="H27" s="4">
+        <v>1.14329869269695E-2</v>
+      </c>
+      <c r="I27" s="4">
+        <v>9.4617822843900898E-3</v>
+      </c>
+      <c r="J27" s="4">
+        <v>79.590935612571499</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" t="str">
+        <f t="shared" si="7"/>
+        <v>i</v>
+      </c>
+      <c r="B28" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28">
+        <v>51.291533281819099</v>
+      </c>
+      <c r="D28">
+        <v>0.63479097345970004</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C29">
+        <v>0.124185892482614</v>
+      </c>
+      <c r="D29">
+        <v>0.58989087411098595</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" t="str">
+        <f t="shared" ref="A30:A67" si="8">A29</f>
+        <v>j</v>
+      </c>
+      <c r="B30" t="s">
+        <v>51</v>
+      </c>
+      <c r="C30">
+        <v>9.3864822670430303</v>
+      </c>
+      <c r="D30">
+        <v>0.58579865327298797</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" t="str">
+        <f t="shared" si="8"/>
+        <v>j</v>
+      </c>
+      <c r="B31" t="s">
+        <v>52</v>
+      </c>
+      <c r="C31">
+        <v>50.228265497610799</v>
+      </c>
+      <c r="D31">
+        <v>0.58426899847034497</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>35</v>
+      </c>
+      <c r="B32" t="s">
+        <v>50</v>
+      </c>
+      <c r="C32">
+        <v>-9.6194786557962403E-2</v>
+      </c>
+      <c r="D32">
+        <v>0.54308264866825395</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="str">
+        <f t="shared" ref="A33:A67" si="9">A32</f>
+        <v>k</v>
+      </c>
+      <c r="B33" t="s">
+        <v>51</v>
+      </c>
+      <c r="C33">
+        <v>48.744342642675697</v>
+      </c>
+      <c r="D33">
+        <v>0.535635437528582</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="str">
+        <f t="shared" si="9"/>
+        <v>k</v>
+      </c>
+      <c r="B34" t="s">
+        <v>52</v>
+      </c>
+      <c r="C34">
+        <v>48.746708088246798</v>
+      </c>
+      <c r="D34">
+        <v>0.54687130399129502</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" t="s">
+        <v>50</v>
+      </c>
+      <c r="C35">
+        <v>0.105262327913834</v>
+      </c>
+      <c r="D35">
+        <v>0.50000394240928503</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="str">
+        <f t="shared" ref="A36:A67" si="10">A35</f>
+        <v>l</v>
+      </c>
+      <c r="B36" t="s">
+        <v>51</v>
+      </c>
+      <c r="C36">
+        <v>45.789112642517999</v>
+      </c>
+      <c r="D36">
+        <v>0.49829293677952402</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" t="str">
+        <f t="shared" si="10"/>
+        <v>l</v>
+      </c>
+      <c r="B37" t="s">
+        <v>52</v>
+      </c>
+      <c r="C37">
+        <v>49.577767965559097</v>
+      </c>
+      <c r="D37">
+        <v>0.494405721224354</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>50</v>
+      </c>
+      <c r="C38">
+        <v>0.30553671960008399</v>
+      </c>
+      <c r="D38">
+        <v>0.45130730291895899</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" t="str">
+        <f t="shared" ref="A39:A67" si="11">A38</f>
+        <v>m</v>
+      </c>
+      <c r="B39" t="s">
+        <v>51</v>
+      </c>
+      <c r="C39">
+        <v>41.5695519846088</v>
+      </c>
+      <c r="D39">
+        <v>0.45537981171053199</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" t="str">
+        <f t="shared" si="11"/>
+        <v>m</v>
+      </c>
+      <c r="B40" t="s">
+        <v>52</v>
+      </c>
+      <c r="C40">
+        <v>46.200700171888997</v>
+      </c>
+      <c r="D40">
+        <v>0.453333701291533</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>38</v>
+      </c>
+      <c r="B41" t="s">
+        <v>50</v>
+      </c>
+      <c r="C41">
+        <v>-0.124974374339647</v>
+      </c>
+      <c r="D41">
+        <v>0.40637960670524897</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" t="str">
+        <f t="shared" ref="A42:A67" si="12">A41</f>
+        <v>n</v>
+      </c>
+      <c r="B42" t="s">
+        <v>51</v>
+      </c>
+      <c r="C42">
+        <v>37.558544777884599</v>
+      </c>
+      <c r="D42">
+        <v>0.40309557977070898</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" t="str">
+        <f t="shared" si="12"/>
+        <v>n</v>
+      </c>
+      <c r="B43" t="s">
+        <v>52</v>
+      </c>
+      <c r="C43">
+        <v>46.821629634302099</v>
+      </c>
+      <c r="D43">
+        <v>0.40274864775361502</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" t="s">
+        <v>50</v>
+      </c>
+      <c r="C44">
+        <v>0.28661315503130402</v>
+      </c>
+      <c r="D44">
+        <v>0.36142037121725801</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" t="str">
+        <f t="shared" ref="A45:A67" si="13">A44</f>
+        <v>o</v>
+      </c>
+      <c r="B45" t="s">
+        <v>51</v>
+      </c>
+      <c r="C45">
+        <v>33.340166842760901</v>
+      </c>
+      <c r="D45">
+        <v>0.36580038793307301</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" t="str">
+        <f t="shared" si="13"/>
+        <v>o</v>
+      </c>
+      <c r="B46" t="s">
+        <v>52</v>
+      </c>
+      <c r="C46">
+        <v>48.286628924668399</v>
+      </c>
+      <c r="D46">
+        <v>0.36149527699367601</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>40</v>
+      </c>
+      <c r="B47" t="s">
+        <v>50</v>
+      </c>
+      <c r="C47">
+        <v>6.7415198776274096E-2</v>
+      </c>
+      <c r="D47">
+        <v>0.32023007900588102</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" t="str">
+        <f t="shared" ref="A48:A67" si="14">A47</f>
+        <v>p</v>
+      </c>
+      <c r="B48" t="s">
+        <v>51</v>
+      </c>
+      <c r="C48">
+        <v>29.752180152334599</v>
+      </c>
+      <c r="D48">
+        <v>0.32286360840836997</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" t="str">
+        <f t="shared" si="14"/>
+        <v>p</v>
+      </c>
+      <c r="B49" t="s">
+        <v>52</v>
+      </c>
+      <c r="C49">
+        <v>48.908741109867002</v>
+      </c>
+      <c r="D49">
+        <v>0.31652815668711398</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>41</v>
+      </c>
+      <c r="B50" t="s">
+        <v>50</v>
+      </c>
+      <c r="C50">
+        <v>-0.15257123933578101</v>
+      </c>
+      <c r="D50">
+        <v>0.275294497973601</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" t="str">
+        <f t="shared" ref="A51:A67" si="15">A50</f>
+        <v>q</v>
+      </c>
+      <c r="B51" t="s">
+        <v>51</v>
+      </c>
+      <c r="C51">
+        <v>25.5322252534969</v>
+      </c>
+      <c r="D51">
+        <v>0.27807783892892601</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" t="str">
+        <f t="shared" si="15"/>
+        <v>q</v>
+      </c>
+      <c r="B52" t="s">
+        <v>52</v>
+      </c>
+      <c r="C52">
+        <v>66.5845331398924</v>
+      </c>
+      <c r="D52">
+        <v>0.27654029930771201</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>42</v>
+      </c>
+      <c r="B53" t="s">
+        <v>50</v>
+      </c>
+      <c r="C53">
+        <v>-0.162033021620171</v>
+      </c>
+      <c r="D53">
+        <v>0.23035103212274999</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" t="str">
+        <f t="shared" ref="A54:A67" si="16">A53</f>
+        <v>r</v>
+      </c>
+      <c r="B54" t="s">
+        <v>51</v>
+      </c>
+      <c r="C54">
+        <v>21.7321369435289</v>
+      </c>
+      <c r="D54">
+        <v>0.22765836658098401</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" t="str">
+        <f t="shared" si="16"/>
+        <v>r</v>
+      </c>
+      <c r="B55" t="s">
+        <v>52</v>
+      </c>
+      <c r="C55">
+        <v>68.890842571712398</v>
+      </c>
+      <c r="D55">
+        <v>0.23151010045258799</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>43</v>
+      </c>
+      <c r="B56" t="s">
+        <v>50</v>
+      </c>
+      <c r="C56">
+        <v>-0.17149480390456101</v>
+      </c>
+      <c r="D56">
+        <v>0.185407566271899</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" t="str">
+        <f t="shared" ref="A57:A67" si="17">A56</f>
+        <v>s</v>
+      </c>
+      <c r="B57" t="s">
+        <v>51</v>
+      </c>
+      <c r="C57">
+        <v>17.934019838203501</v>
+      </c>
+      <c r="D57">
+        <v>0.18660211628530399</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" t="str">
+        <f t="shared" si="17"/>
+        <v>s</v>
+      </c>
+      <c r="B58" t="s">
+        <v>52</v>
+      </c>
+      <c r="C58">
+        <v>73.092662387838402</v>
+      </c>
+      <c r="D58">
+        <v>0.190154227051235</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>44</v>
+      </c>
+      <c r="B59" t="s">
+        <v>50</v>
+      </c>
+      <c r="C59">
+        <v>-0.18056234526043699</v>
+      </c>
+      <c r="D59">
+        <v>0.14233674483150099</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" t="str">
+        <f t="shared" ref="A60:A67" si="18">A59</f>
+        <v>t</v>
+      </c>
+      <c r="B60" t="s">
+        <v>51</v>
+      </c>
+      <c r="C60">
+        <v>13.503540283537999</v>
+      </c>
+      <c r="D60">
+        <v>0.14182423162443</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" t="str">
+        <f t="shared" si="18"/>
+        <v>t</v>
+      </c>
+      <c r="B61" t="s">
+        <v>52</v>
+      </c>
+      <c r="C61">
+        <v>76.871855928594996</v>
+      </c>
+      <c r="D61">
+        <v>0.14132354564521399</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>45</v>
+      </c>
+      <c r="B62" t="s">
+        <v>50</v>
+      </c>
+      <c r="C62">
+        <v>2.0500528282841601E-2</v>
+      </c>
+      <c r="D62">
+        <v>9.7385394162080099E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" t="str">
+        <f t="shared" ref="A63:A67" si="19">A62</f>
+        <v>u</v>
+      </c>
+      <c r="B63" t="s">
+        <v>51</v>
+      </c>
+      <c r="C63">
+        <v>9.4937157995994408</v>
+      </c>
+      <c r="D63">
+        <v>9.51579329159635E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" t="str">
+        <f t="shared" si="19"/>
+        <v>u</v>
+      </c>
+      <c r="B64" t="s">
+        <v>52</v>
+      </c>
+      <c r="C64">
+        <v>81.283411918691698</v>
+      </c>
+      <c r="D64">
+        <v>9.6214498604387105E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>46</v>
+      </c>
+      <c r="B65" t="s">
+        <v>50</v>
+      </c>
+      <c r="C65">
+        <v>1.14329869269695E-2</v>
+      </c>
+      <c r="D65">
+        <v>5.4314572721681303E-2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" t="str">
+        <f t="shared" ref="A66:A67" si="20">A65</f>
+        <v>v</v>
+      </c>
+      <c r="B66" t="s">
+        <v>51</v>
+      </c>
+      <c r="C66">
+        <v>9.4617822843900898E-3</v>
+      </c>
+      <c r="D66">
+        <v>4.4951350669420999E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" t="str">
+        <f t="shared" si="20"/>
+        <v>v</v>
+      </c>
+      <c r="B67" t="s">
+        <v>52</v>
+      </c>
+      <c r="C67">
+        <v>79.590935612571499</v>
+      </c>
+      <c r="D67">
+        <v>5.6952044533455197E-2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
